--- a/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
@@ -58804,13 +58804,13 @@
       </c>
       <c r="EA121" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EB121" t="inlineStr"/>
       <c r="EC121" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED121" t="inlineStr">
@@ -58835,22 +58835,22 @@
       </c>
       <c r="EH121" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EI121" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ121" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="EK121" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EL121" t="inlineStr">
@@ -58860,7 +58860,7 @@
       </c>
       <c r="EM121" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EN121" t="inlineStr">
@@ -58870,12 +58870,12 @@
       </c>
       <c r="EO121" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EP121" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
-  <autoFilter ref="A1:EP121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP122" headerRowCount="1">
+  <autoFilter ref="A1:EP122"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP121"/>
+  <dimension ref="A1:EP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE7" t="n">
         <v>0.83</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="DD31" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE31" t="n">
         <v>0.83</v>
@@ -19981,7 +19981,7 @@
         <v>2.14</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -20902,7 +20902,7 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE42" t="n">
         <v>1.33</v>
@@ -25669,7 +25669,7 @@
         <v>0.5</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -30477,7 +30477,7 @@
         <v>0.5</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF62" t="n">
         <v>0.33</v>
@@ -32366,7 +32366,7 @@
         <v>59</v>
       </c>
       <c r="DD66" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE66" t="n">
         <v>1.33</v>
@@ -41506,7 +41506,7 @@
         <v>63</v>
       </c>
       <c r="DD85" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE85" t="n">
         <v>0.5</v>
@@ -43897,7 +43897,7 @@
         <v>0.83</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF90" t="n">
         <v>1</v>
@@ -49859,12 +49859,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
@@ -49880,19 +49880,19 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -49907,92 +49907,92 @@
         <v>2</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W103" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X103" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y103" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="Z103" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Stadio Comunale Via del Mare</t>
+          <t>Stadio Giuseppe Sinigaglia</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>Viale dello Stadio, Lecce</t>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
         </is>
       </c>
       <c r="AC103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AI103" t="n">
-        <v>2.71</v>
+        <v>1.9</v>
       </c>
       <c r="AJ103" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK103" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AL103" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM103" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AN103" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AO103" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR103" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="AS103" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="AT103" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AU103" t="n">
         <v>0</v>
@@ -50022,7 +50022,7 @@
         <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE103" t="n">
         <v>0</v>
@@ -50037,13 +50037,13 @@
         <v>1</v>
       </c>
       <c r="BI103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL103" t="n">
         <v>0</v>
@@ -50052,49 +50052,49 @@
         <v>5</v>
       </c>
       <c r="BN103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
         <v>4</v>
       </c>
-      <c r="BO103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR103" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS103" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT103" t="n">
-        <v>3</v>
-      </c>
       <c r="BU103" t="n">
         <v>1</v>
       </c>
       <c r="BV103" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="BW103" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="BX103" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="BY103" t="n">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="BZ103" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="CA103" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="CB103" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="CC103" t="n">
         <v>0</v>
@@ -50142,73 +50142,73 @@
         <v>1</v>
       </c>
       <c r="CR103" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="CS103" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT103" t="n">
         <v>1</v>
       </c>
       <c r="CU103" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CV103" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>30</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK103" t="n">
         <v>10</v>
       </c>
-      <c r="CW103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX103" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY103" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ103" t="n">
-        <v>40</v>
-      </c>
-      <c r="DA103" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB103" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC103" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD103" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DE103" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF103" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DG103" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DH103" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="DI103" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DJ103" t="n">
-        <v>60</v>
-      </c>
-      <c r="DK103" t="n">
-        <v>30</v>
-      </c>
       <c r="DL103" t="n">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
       <c r="DM103" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="DN103" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="DO103" t="n">
         <v>12</v>
@@ -50235,87 +50235,99 @@
         <v>0</v>
       </c>
       <c r="DW103" t="n">
-        <v>19</v>
+        <v>13.12</v>
       </c>
       <c r="DX103" t="n">
-        <v>6.57</v>
+        <v>2.07</v>
       </c>
       <c r="DY103" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ103" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="EA103" t="inlineStr">
         <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="EB103" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
       <c r="EC103" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED103" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EE103" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EF103" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EG103" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EH103" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EI103" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EJ103" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EK103" t="inlineStr">
         <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EL103" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL103" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EM103" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EN103" t="inlineStr"/>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EN103" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EO103" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EP103" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -50335,12 +50347,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
@@ -50356,19 +50368,19 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -50383,92 +50395,92 @@
         <v>2</v>
       </c>
       <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3</v>
+      </c>
+      <c r="U104" t="n">
+        <v>11</v>
+      </c>
+      <c r="V104" t="n">
+        <v>5</v>
+      </c>
+      <c r="W104" t="n">
+        <v>10</v>
+      </c>
+      <c r="X104" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Stadio Comunale Via del Mare</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Viale dello Stadio, Lecce</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="n">
         <v>4</v>
       </c>
-      <c r="T104" t="n">
-        <v>2</v>
-      </c>
-      <c r="U104" t="n">
-        <v>10</v>
-      </c>
-      <c r="V104" t="n">
-        <v>4</v>
-      </c>
-      <c r="W104" t="n">
-        <v>21</v>
-      </c>
-      <c r="X104" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sinigaglia, 3, Como</t>
-        </is>
-      </c>
-      <c r="AC104" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>1</v>
-      </c>
       <c r="AE104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ104" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF104" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR104" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="AS104" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="AT104" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU104" t="n">
         <v>0</v>
@@ -50498,7 +50510,7 @@
         <v>0</v>
       </c>
       <c r="BD104" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE104" t="n">
         <v>0</v>
@@ -50513,13 +50525,13 @@
         <v>1</v>
       </c>
       <c r="BI104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL104" t="n">
         <v>0</v>
@@ -50528,49 +50540,49 @@
         <v>5</v>
       </c>
       <c r="BN104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BO104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU104" t="n">
         <v>1</v>
       </c>
       <c r="BV104" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BW104" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="BX104" t="n">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="BY104" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="BZ104" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="CA104" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="CB104" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="CC104" t="n">
         <v>0</v>
@@ -50618,73 +50630,73 @@
         <v>1</v>
       </c>
       <c r="CR104" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="CS104" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CT104" t="n">
         <v>1</v>
       </c>
       <c r="CU104" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CV104" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CW104" t="n">
         <v>1</v>
       </c>
       <c r="CX104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CY104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ104" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK104" t="n">
         <v>30</v>
       </c>
-      <c r="DA104" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB104" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC104" t="n">
-        <v>70</v>
-      </c>
-      <c r="DD104" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE104" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF104" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DG104" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH104" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DI104" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="DJ104" t="n">
-        <v>70</v>
-      </c>
-      <c r="DK104" t="n">
-        <v>10</v>
-      </c>
       <c r="DL104" t="n">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="DM104" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="DN104" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="DO104" t="n">
         <v>12</v>
@@ -50711,99 +50723,87 @@
         <v>0</v>
       </c>
       <c r="DW104" t="n">
-        <v>13.12</v>
+        <v>19</v>
       </c>
       <c r="DX104" t="n">
-        <v>2.07</v>
+        <v>6.57</v>
       </c>
       <c r="DY104" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ104" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA104" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EB104" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr"/>
       <c r="EC104" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="ED104" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EE104" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EF104" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EG104" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH104" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI104" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EJ104" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EK104" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EL104" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr"/>
       <c r="EM104" t="inlineStr">
         <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EN104" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr"/>
       <c r="EO104" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EP104" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
@@ -52105,7 +52105,7 @@
         <v>1.17</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF107" t="n">
         <v>1.4</v>
@@ -54131,116 +54131,116 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
         <v>45983.58333333334</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
         <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K112" t="n">
         <v>2</v>
       </c>
       <c r="L112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T112" t="n">
         <v>5</v>
       </c>
       <c r="U112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V112" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W112" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X112" t="n">
         <v>16</v>
       </c>
       <c r="Y112" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z112" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Dacia Arena</t>
+          <t>Sardegna Arena</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Piazza le Repubblica Argentina, 3, Udine</t>
+          <t>Via Raimondo Carta Raspi, Cagliari</t>
         </is>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE112" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AF112" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="AG112" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AI112" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AJ112" t="n">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="AK112" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="AL112" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AM112" t="n">
         <v>1.7</v>
@@ -54249,52 +54249,52 @@
         <v>2.42</v>
       </c>
       <c r="AO112" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AR112" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AS112" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="AT112" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB112" t="n">
-        <v>467</v>
+        <v>-1</v>
       </c>
       <c r="BC112" t="n">
         <v>0</v>
       </c>
       <c r="BD112" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BE112" t="n">
         <v>0</v>
@@ -54309,64 +54309,64 @@
         <v>1</v>
       </c>
       <c r="BI112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BJ112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM112" t="n">
         <v>5</v>
       </c>
       <c r="BN112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP112" t="n">
         <v>1</v>
       </c>
       <c r="BQ112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU112" t="n">
         <v>1</v>
       </c>
       <c r="BV112" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BW112" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BX112" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="BY112" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="BZ112" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CA112" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="CB112" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="CC112" t="n">
         <v>0</v>
@@ -54399,7 +54399,7 @@
         <v>0</v>
       </c>
       <c r="CM112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN112" t="n">
         <v>0</v>
@@ -54408,16 +54408,16 @@
         <v>0</v>
       </c>
       <c r="CP112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ112" t="n">
         <v>1</v>
       </c>
       <c r="CR112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS112" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CT112" t="n">
         <v>1</v>
@@ -54426,61 +54426,61 @@
         <v>16</v>
       </c>
       <c r="CV112" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="CW112" t="n">
         <v>1</v>
       </c>
       <c r="CX112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ112" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DA112" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB112" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DC112" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="DF112" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG112" t="n">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="DH112" t="n">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="DI112" t="n">
-        <v>1.91</v>
+        <v>0.64</v>
       </c>
       <c r="DJ112" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="DK112" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL112" t="n">
-        <v>1.46</v>
+        <v>0.99</v>
       </c>
       <c r="DM112" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="DN112" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="DO112" t="n">
         <v>12</v>
@@ -54495,26 +54495,26 @@
         <v>1</v>
       </c>
       <c r="DS112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW112" t="n">
-        <v>3.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DX112" t="n">
-        <v>4.58</v>
+        <v>13.07</v>
       </c>
       <c r="DY112" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="DZ112" t="inlineStr">
@@ -54524,78 +54524,62 @@
       </c>
       <c r="EA112" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EB112" t="inlineStr"/>
       <c r="EC112" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="ED112" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EE112" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF112" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG112" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EH112" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EI112" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ112" t="inlineStr">
         <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EK112" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EL112" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EM112" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EN112" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EK112" t="inlineStr"/>
+      <c r="EL112" t="inlineStr"/>
+      <c r="EM112" t="inlineStr"/>
+      <c r="EN112" t="inlineStr"/>
       <c r="EO112" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EP112" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
@@ -54615,116 +54599,116 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
         <v>45983.58333333334</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K113" t="n">
         <v>2</v>
       </c>
       <c r="L113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
+        <v>3</v>
+      </c>
+      <c r="R113" t="n">
         <v>5</v>
       </c>
-      <c r="R113" t="n">
-        <v>8</v>
-      </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T113" t="n">
         <v>5</v>
       </c>
       <c r="U113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V113" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W113" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="X113" t="n">
         <v>16</v>
       </c>
       <c r="Y113" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Z113" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Sardegna Arena</t>
+          <t>Dacia Arena</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Via Raimondo Carta Raspi, Cagliari</t>
+          <t>Piazza le Repubblica Argentina, 3, Udine</t>
         </is>
       </c>
       <c r="AC113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI113" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AJ113" t="n">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK113" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AL113" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AM113" t="n">
         <v>1.7</v>
@@ -54733,52 +54717,52 @@
         <v>2.42</v>
       </c>
       <c r="AO113" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AR113" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AS113" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AU113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>-1</v>
+        <v>467</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -54793,64 +54777,64 @@
         <v>1</v>
       </c>
       <c r="BI113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM113" t="n">
         <v>5</v>
       </c>
       <c r="BN113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP113" t="n">
         <v>1</v>
       </c>
       <c r="BQ113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU113" t="n">
         <v>1</v>
       </c>
       <c r="BV113" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW113" t="n">
         <v>34</v>
       </c>
-      <c r="BW113" t="n">
-        <v>35</v>
-      </c>
       <c r="BX113" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="BY113" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="BZ113" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -54883,7 +54867,7 @@
         <v>0</v>
       </c>
       <c r="CM113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN113" t="n">
         <v>0</v>
@@ -54892,16 +54876,16 @@
         <v>0</v>
       </c>
       <c r="CP113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ113" t="n">
         <v>1</v>
       </c>
       <c r="CR113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS113" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CT113" t="n">
         <v>1</v>
@@ -54910,61 +54894,61 @@
         <v>16</v>
       </c>
       <c r="CV113" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
       </c>
       <c r="CX113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY113" t="n">
         <v>7</v>
       </c>
-      <c r="CY113" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ113" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DA113" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DC113" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF113" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="DG113" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="DH113" t="n">
-        <v>0.91</v>
+        <v>1.36</v>
       </c>
       <c r="DI113" t="n">
-        <v>0.64</v>
+        <v>1.91</v>
       </c>
       <c r="DJ113" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="DK113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL113" t="n">
-        <v>0.99</v>
+        <v>1.46</v>
       </c>
       <c r="DM113" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="DN113" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="DO113" t="n">
         <v>12</v>
@@ -54979,26 +54963,26 @@
         <v>1</v>
       </c>
       <c r="DS113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW113" t="n">
-        <v>9.859999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="DX113" t="n">
-        <v>13.07</v>
+        <v>4.58</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
@@ -55008,62 +54992,78 @@
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr"/>
       <c r="EC113" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="ED113" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EE113" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF113" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG113" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EI113" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EJ113" t="inlineStr">
         <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EK113" t="inlineStr"/>
-      <c r="EL113" t="inlineStr"/>
-      <c r="EM113" t="inlineStr"/>
-      <c r="EN113" t="inlineStr"/>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EM113" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN113" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
       <c r="EO113" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EP113" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.79</t>
         </is>
       </c>
     </row>
@@ -58876,6 +58876,494 @@
       <c r="EP121" t="inlineStr">
         <is>
           <t>1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Italy_Serie_A_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>13</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45989.82291666666</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4</v>
+      </c>
+      <c r="K122" t="n">
+        <v>4</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>13</v>
+      </c>
+      <c r="R122" t="n">
+        <v>5</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="n">
+        <v>7</v>
+      </c>
+      <c r="U122" t="n">
+        <v>18</v>
+      </c>
+      <c r="V122" t="n">
+        <v>12</v>
+      </c>
+      <c r="W122" t="n">
+        <v>11</v>
+      </c>
+      <c r="X122" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>518</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW122" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="DX122" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED122" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EE122" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EF122" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="EK122" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EL122" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EM122" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EN122" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EO122" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP122" t="inlineStr">
+        <is>
+          <t>2.06</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP150" headerRowCount="1">
-  <autoFilter ref="A1:EP150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP151" headerRowCount="1">
+  <autoFilter ref="A1:EP151"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP150"/>
+  <dimension ref="A1:EP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE5" t="n">
         <v>1.5</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -7557,7 +7557,7 @@
         <v>1.86</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -12806,7 +12806,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE25" t="n">
         <v>0.86</v>
@@ -12839,7 +12839,7 @@
         <v>2.66</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -15675,7 +15675,7 @@
         <v>2.05</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -18063,7 +18063,7 @@
         <v>3.61</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19493,7 +19493,7 @@
         <v>0.29</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF39" t="n">
         <v>0</v>
@@ -19523,7 +19523,7 @@
         <v>3.03</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20935,7 +20935,7 @@
         <v>2.37</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -22814,7 +22814,7 @@
         <v>25</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE46" t="n">
         <v>0.75</v>
@@ -22847,7 +22847,7 @@
         <v>2.95</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -27585,7 +27585,7 @@
         <v>1.63</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF56" t="n">
         <v>2</v>
@@ -27615,7 +27615,7 @@
         <v>3.89</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -29071,7 +29071,7 @@
         <v>2.82</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -31894,7 +31894,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE65" t="n">
         <v>2.14</v>
@@ -31927,7 +31927,7 @@
         <v>3.63</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32399,7 +32399,7 @@
         <v>2.96</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -36209,7 +36209,7 @@
         <v>0.75</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF74" t="n">
         <v>1.33</v>
@@ -36239,7 +36239,7 @@
         <v>2.63</v>
       </c>
       <c r="DO74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP74" t="b">
         <v>0</v>
@@ -37811,40 +37811,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M78" t="n">
         <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -37853,128 +37853,128 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S78" t="n">
+        <v>4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
         <v>10</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>7</v>
       </c>
-      <c r="U78" t="n">
-        <v>11</v>
-      </c>
-      <c r="V78" t="n">
-        <v>15</v>
-      </c>
       <c r="W78" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X78" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y78" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z78" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>MAPEI Stadium - Città del Tricolore</t>
+          <t>Stadio Marc'Antonio Bentegodi</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Piazza Azzuri d'Italia, 1, Reggio nell'Emilia</t>
+          <t>Piazzale Olimpia, Verona</t>
         </is>
       </c>
       <c r="AC78" t="n">
         <v>3</v>
       </c>
       <c r="AD78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE78" t="n">
-        <v>3.85</v>
+        <v>2.11</v>
       </c>
       <c r="AF78" t="n">
-        <v>3.48</v>
+        <v>2.83</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI78" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AJ78" t="n">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL78" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AN78" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AO78" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AU78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA78" t="n">
         <v>1</v>
       </c>
       <c r="BB78" t="n">
-        <v>113</v>
+        <v>-1</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37989,64 +37989,64 @@
         <v>1</v>
       </c>
       <c r="BI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN78" t="n">
         <v>3</v>
       </c>
-      <c r="BJ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL78" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM78" t="n">
+      <c r="BO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR78" t="n">
         <v>4</v>
       </c>
-      <c r="BN78" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO78" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR78" t="n">
-        <v>1</v>
-      </c>
       <c r="BS78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="BW78" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="BX78" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BY78" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
       <c r="CB78" t="n">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="CC78" t="n">
         <v>0</v>
@@ -38094,31 +38094,31 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS78" t="n">
         <v>21</v>
       </c>
-      <c r="CS78" t="n">
-        <v>19</v>
-      </c>
       <c r="CT78" t="n">
         <v>1</v>
       </c>
       <c r="CU78" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV78" t="n">
         <v>16</v>
       </c>
-      <c r="CV78" t="n">
-        <v>18</v>
-      </c>
       <c r="CW78" t="n">
         <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CZ78" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DA78" t="n">
         <v>50</v>
@@ -38127,55 +38127,55 @@
         <v>33</v>
       </c>
       <c r="DC78" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="DE78" t="n">
-        <v>2.14</v>
+        <v>0.75</v>
       </c>
       <c r="DF78" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DG78" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="DH78" t="n">
-        <v>1.43</v>
+        <v>0.57</v>
       </c>
       <c r="DI78" t="n">
-        <v>2.14</v>
+        <v>1.14</v>
       </c>
       <c r="DJ78" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DK78" t="n">
         <v>50</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.07</v>
+        <v>1.88</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="DO78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
       </c>
       <c r="DQ78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT78" t="b">
         <v>0</v>
@@ -38184,98 +38184,74 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW78" t="n">
-        <v>14.95</v>
+        <v>14.97</v>
       </c>
       <c r="DX78" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr"/>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED78" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EE78" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EG78" t="inlineStr">
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr"/>
+      <c r="EE78" t="inlineStr"/>
+      <c r="EF78" t="inlineStr"/>
+      <c r="EG78" t="inlineStr"/>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr"/>
+      <c r="EM78" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EN78" t="inlineStr"/>
+      <c r="EO78" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EP78" t="inlineStr">
         <is>
           <t>1.79</t>
-        </is>
-      </c>
-      <c r="EH78" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>4.47</t>
-        </is>
-      </c>
-      <c r="EJ78" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EK78" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EL78" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM78" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EN78" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EO78" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EP78" t="inlineStr">
-        <is>
-          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -38295,40 +38271,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L79" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -38337,128 +38313,128 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W79" t="n">
+        <v>18</v>
+      </c>
+      <c r="X79" t="n">
         <v>16</v>
       </c>
-      <c r="X79" t="n">
-        <v>12</v>
-      </c>
       <c r="Y79" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Z79" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi</t>
+          <t>MAPEI Stadium - Città del Tricolore</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Piazzale Olimpia, Verona</t>
+          <t>Piazza Azzuri d'Italia, 1, Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="AC79" t="n">
         <v>3</v>
       </c>
       <c r="AD79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.11</v>
+        <v>3.85</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AI79" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ79" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="AK79" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AN79" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AO79" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AR79" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AU79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA79" t="n">
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>-1</v>
+        <v>113</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38473,136 +38449,136 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ79" t="n">
         <v>1</v>
       </c>
       <c r="BK79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN79" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS79" t="n">
         <v>3</v>
       </c>
-      <c r="BO79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>1</v>
-      </c>
       <c r="BT79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="BW79" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ79" t="n">
         <v>33</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>110</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>128</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ79" t="n">
-        <v>17</v>
       </c>
       <c r="DA79" t="n">
         <v>50</v>
@@ -38611,40 +38587,40 @@
         <v>33</v>
       </c>
       <c r="DC79" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DD79" t="n">
-        <v>0.86</v>
+        <v>1.43</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.75</v>
+        <v>2.14</v>
       </c>
       <c r="DF79" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DG79" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.57</v>
+        <v>1.43</v>
       </c>
       <c r="DI79" t="n">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="DJ79" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DK79" t="n">
         <v>50</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="DO79" t="n">
         <v>15</v>
@@ -38653,13 +38629,13 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT79" t="b">
         <v>0</v>
@@ -38668,74 +38644,98 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>14.97</v>
+        <v>14.95</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr"/>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="ED79" t="inlineStr"/>
-      <c r="EE79" t="inlineStr"/>
-      <c r="EF79" t="inlineStr"/>
-      <c r="EG79" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr"/>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -40699,34 +40699,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>45959.72916666666</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
         <v>1</v>
       </c>
       <c r="I84" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
         <v>3</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2</v>
-      </c>
       <c r="L84" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M84" t="n">
         <v>1</v>
@@ -40741,43 +40741,43 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U84" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V84" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X84" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Y84" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="Z84" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Stadio Olimpico</t>
+          <t>Stadio Giuseppe Sinigaglia</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
         </is>
       </c>
       <c r="AC84" t="n">
@@ -40787,82 +40787,82 @@
         <v>4</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF84" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AG84" t="n">
-        <v>7.5</v>
+        <v>6.35</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AJ84" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AK84" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AL84" t="n">
         <v>1.7</v>
       </c>
       <c r="AM84" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AO84" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AQ84" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT84" t="n">
         <v>1.36</v>
       </c>
-      <c r="AR84" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AU84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX84" t="n">
         <v>2</v>
       </c>
       <c r="AY84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB84" t="n">
-        <v>113</v>
+        <v>518</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40877,22 +40877,22 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ84" t="n">
         <v>3</v>
       </c>
-      <c r="BJ84" t="n">
-        <v>1</v>
-      </c>
       <c r="BK84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM84" t="n">
         <v>4</v>
       </c>
       <c r="BN84" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BO84" t="n">
         <v>0</v>
@@ -40916,25 +40916,25 @@
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="BW84" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BX84" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="BY84" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="BZ84" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="CA84" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="CB84" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
@@ -40961,13 +40961,13 @@
         <v>1</v>
       </c>
       <c r="CK84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL84" t="n">
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN84" t="n">
         <v>0</v>
@@ -40982,19 +40982,19 @@
         <v>1</v>
       </c>
       <c r="CR84" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CS84" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="CT84" t="n">
         <v>1</v>
       </c>
       <c r="CU84" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="CV84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW84" t="n">
         <v>1</v>
@@ -41006,52 +41006,52 @@
         <v>9</v>
       </c>
       <c r="CZ84" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DA84" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="DB84" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DC84" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="DF84" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG84" t="n">
         <v>0.5</v>
       </c>
       <c r="DH84" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="DI84" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="DJ84" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DK84" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DO84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41063,7 +41063,7 @@
         <v>1</v>
       </c>
       <c r="DS84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT84" t="b">
         <v>0</v>
@@ -41075,99 +41075,99 @@
         <v>1</v>
       </c>
       <c r="DW84" t="n">
-        <v>19.56</v>
+        <v>11.27</v>
       </c>
       <c r="DX84" t="n">
-        <v>5.19</v>
+        <v>1.81</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="EC84" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="ED84" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EH84" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EI84" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ84" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="EK84" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL84" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EM84" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="EN84" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EO84" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EP84" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -41187,12 +41187,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
@@ -41208,13 +41208,13 @@
         <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M85" t="n">
         <v>1</v>
@@ -41229,45 +41229,37 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R85" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="V85" t="n">
+        <v>8</v>
+      </c>
+      <c r="W85" t="n">
+        <v>12</v>
+      </c>
+      <c r="X85" t="n">
         <v>13</v>
       </c>
-      <c r="W85" t="n">
-        <v>11</v>
-      </c>
-      <c r="X85" t="n">
-        <v>21</v>
-      </c>
       <c r="Y85" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Z85" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sinigaglia, 3, Como</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
         <v>1</v>
       </c>
@@ -41275,52 +41267,52 @@
         <v>4</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AF85" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AG85" t="n">
-        <v>6.35</v>
+        <v>8</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI85" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AJ85" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AK85" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="AO85" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR85" t="n">
-        <v>3.23</v>
+        <v>2.5</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU85" t="n">
         <v>4</v>
@@ -41344,13 +41336,13 @@
         <v>2</v>
       </c>
       <c r="BB85" t="n">
-        <v>518</v>
+        <v>90</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -41365,22 +41357,22 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL85" t="n">
         <v>3</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>0</v>
       </c>
       <c r="BM85" t="n">
         <v>4</v>
       </c>
       <c r="BN85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO85" t="n">
         <v>0</v>
@@ -41404,34 +41396,34 @@
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="BW85" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BX85" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="BY85" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.65</v>
+        <v>0.85</v>
       </c>
       <c r="CB85" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="CC85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CD85" t="n">
         <v>0</v>
       </c>
       <c r="CE85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF85" t="n">
         <v>0</v>
@@ -41455,7 +41447,7 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN85" t="n">
         <v>0</v>
@@ -41464,82 +41456,82 @@
         <v>0</v>
       </c>
       <c r="CP85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ85" t="n">
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS85" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
       </c>
       <c r="CU85" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CV85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CW85" t="n">
         <v>1</v>
       </c>
       <c r="CX85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CY85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ85" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DA85" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DB85" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DC85" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DD85" t="n">
         <v>2.14</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.75</v>
+        <v>1.43</v>
       </c>
       <c r="DF85" t="n">
         <v>2</v>
       </c>
       <c r="DG85" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="DI85" t="n">
-        <v>0.63</v>
+        <v>1.5</v>
       </c>
       <c r="DJ85" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DK85" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="DO85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41563,99 +41555,83 @@
         <v>1</v>
       </c>
       <c r="DW85" t="n">
-        <v>11.27</v>
+        <v>11.6</v>
       </c>
       <c r="DX85" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr"/>
+      <c r="EE85" t="inlineStr"/>
+      <c r="EF85" t="inlineStr"/>
+      <c r="EG85" t="inlineStr"/>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="EE85" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF85" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG85" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="EI85" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EJ85" t="inlineStr">
-        <is>
-          <t>6.94</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EL85" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="EN85" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EO85" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EP85" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -41675,34 +41651,34 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>45959.72916666666</v>
       </c>
       <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
         <v>3</v>
       </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" t="n">
-        <v>4</v>
-      </c>
       <c r="J86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M86" t="n">
         <v>1</v>
@@ -41717,37 +41693,45 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S86" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="V86" t="n">
         <v>8</v>
       </c>
       <c r="W86" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X86" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y86" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Z86" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+        </is>
+      </c>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
@@ -41755,82 +41739,82 @@
         <v>4</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AF86" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="AG86" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AJ86" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK86" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO86" t="n">
         <v>2.05</v>
       </c>
-      <c r="AL86" t="n">
+      <c r="AP86" t="n">
         <v>1.73</v>
       </c>
-      <c r="AM86" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN86" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO86" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AQ86" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR86" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AS86" t="n">
         <v>2.9</v>
       </c>
       <c r="AT86" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AU86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX86" t="n">
         <v>2</v>
       </c>
       <c r="AY86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="BE86" t="n">
         <v>0</v>
@@ -41851,16 +41835,16 @@
         <v>1</v>
       </c>
       <c r="BK86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BL86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM86" t="n">
         <v>4</v>
       </c>
       <c r="BN86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO86" t="n">
         <v>0</v>
@@ -41884,34 +41868,34 @@
         <v>1</v>
       </c>
       <c r="BV86" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BW86" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BX86" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="BY86" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="BZ86" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="CA86" t="n">
-        <v>0.85</v>
+        <v>1.18</v>
       </c>
       <c r="CB86" t="n">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="CC86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD86" t="n">
         <v>0</v>
       </c>
       <c r="CE86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF86" t="n">
         <v>0</v>
@@ -41929,7 +41913,7 @@
         <v>1</v>
       </c>
       <c r="CK86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL86" t="n">
         <v>0</v>
@@ -41944,79 +41928,79 @@
         <v>0</v>
       </c>
       <c r="CP86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ86" t="n">
         <v>1</v>
       </c>
       <c r="CR86" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CS86" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CT86" t="n">
         <v>1</v>
       </c>
       <c r="CU86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CV86" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW86" t="n">
         <v>1</v>
       </c>
       <c r="CX86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA86" t="n">
         <v>38</v>
       </c>
-      <c r="DA86" t="n">
-        <v>75</v>
-      </c>
       <c r="DB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC86" t="n">
         <v>38</v>
       </c>
-      <c r="DC86" t="n">
-        <v>75</v>
-      </c>
       <c r="DD86" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DF86" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG86" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="DH86" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI86" t="n">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="DJ86" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK86" t="n">
         <v>63</v>
       </c>
-      <c r="DK86" t="n">
-        <v>25</v>
-      </c>
       <c r="DL86" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="DN86" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="DO86" t="n">
         <v>15</v>
@@ -42031,7 +42015,7 @@
         <v>1</v>
       </c>
       <c r="DS86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT86" t="b">
         <v>0</v>
@@ -42043,83 +42027,99 @@
         <v>1</v>
       </c>
       <c r="DW86" t="n">
-        <v>11.6</v>
+        <v>19.56</v>
       </c>
       <c r="DX86" t="n">
-        <v>1.65</v>
+        <v>5.19</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="EA86" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EB86" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EC86" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="EB86" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EC86" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="ED86" t="inlineStr"/>
-      <c r="EE86" t="inlineStr"/>
-      <c r="EF86" t="inlineStr"/>
-      <c r="EG86" t="inlineStr"/>
+      <c r="EG86" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH86" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="EK86" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL86" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EM86" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EN86" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EO86" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EP86" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
@@ -42139,170 +42139,170 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45959.82291666666</v>
       </c>
       <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
         <v>3</v>
       </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
         <v>3</v>
       </c>
-      <c r="J87" t="n">
-        <v>8</v>
-      </c>
-      <c r="K87" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>4</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="n">
+        <v>7</v>
+      </c>
+      <c r="U87" t="n">
+        <v>16</v>
+      </c>
+      <c r="V87" t="n">
+        <v>11</v>
+      </c>
+      <c r="W87" t="n">
+        <v>16</v>
+      </c>
+      <c r="X87" t="n">
         <v>13</v>
       </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>8</v>
-      </c>
-      <c r="R87" t="n">
-        <v>2</v>
-      </c>
-      <c r="S87" t="n">
-        <v>14</v>
-      </c>
-      <c r="T87" t="n">
-        <v>8</v>
-      </c>
-      <c r="U87" t="n">
-        <v>22</v>
-      </c>
-      <c r="V87" t="n">
-        <v>10</v>
-      </c>
-      <c r="W87" t="n">
-        <v>11</v>
-      </c>
-      <c r="X87" t="n">
-        <v>16</v>
-      </c>
       <c r="Y87" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza</t>
+          <t>Stadio Comunale Luigi Ferraris</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Via Piccolomini 5, Milano</t>
+          <t>Via Giovanni De Prà, 1, Genova</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.55</v>
+        <v>3.25</v>
       </c>
       <c r="AG87" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.71</v>
+        <v>2.47</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AN87" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AO87" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.45</v>
+        <v>3.27</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB87" t="n">
-        <v>470</v>
+        <v>1046</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -42320,34 +42320,34 @@
         <v>3</v>
       </c>
       <c r="BJ87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL87" t="n">
         <v>2</v>
       </c>
       <c r="BM87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN87" t="n">
         <v>6</v>
       </c>
-      <c r="BN87" t="n">
-        <v>7</v>
-      </c>
       <c r="BO87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP87" t="n">
         <v>0</v>
       </c>
       <c r="BQ87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>3</v>
@@ -42356,34 +42356,34 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BW87" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BX87" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="BY87" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="BZ87" t="n">
-        <v>2.48</v>
+        <v>1.48</v>
       </c>
       <c r="CA87" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.48</v>
+        <v>2.64</v>
       </c>
       <c r="CC87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD87" t="n">
         <v>0</v>
       </c>
       <c r="CE87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF87" t="n">
         <v>0</v>
@@ -42404,13 +42404,13 @@
         <v>0</v>
       </c>
       <c r="CL87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM87" t="n">
         <v>0</v>
       </c>
       <c r="CN87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO87" t="n">
         <v>0</v>
@@ -42422,34 +42422,34 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV87" t="n">
         <v>16</v>
       </c>
-      <c r="CS87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>11</v>
-      </c>
       <c r="CW87" t="n">
         <v>1</v>
       </c>
       <c r="CX87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CZ87" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="DA87" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB87" t="n">
         <v>38</v>
@@ -42458,37 +42458,37 @@
         <v>50</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="DE87" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF87" t="n">
         <v>0.5</v>
       </c>
-      <c r="DF87" t="n">
-        <v>2.25</v>
-      </c>
       <c r="DG87" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="DH87" t="n">
-        <v>1.88</v>
+        <v>0.38</v>
       </c>
       <c r="DI87" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="DJ87" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DK87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL87" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.25</v>
+        <v>2.11</v>
       </c>
       <c r="DO87" t="n">
         <v>15</v>
@@ -42500,7 +42500,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42515,79 +42515,95 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>11.46</v>
+        <v>16.67</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EB87" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EC87" t="inlineStr"/>
-      <c r="ED87" t="inlineStr"/>
-      <c r="EE87" t="inlineStr"/>
-      <c r="EF87" t="inlineStr"/>
-      <c r="EG87" t="inlineStr"/>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr"/>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EI87" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EJ87" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="EK87" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EM87" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EN87" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EO87" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP87" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -42607,12 +42623,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -42622,26 +42638,26 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
         <v>3</v>
       </c>
       <c r="L88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
         <v>3</v>
       </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
@@ -42649,128 +42665,128 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U88" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V88" t="n">
+        <v>8</v>
+      </c>
+      <c r="W88" t="n">
         <v>11</v>
       </c>
-      <c r="W88" t="n">
-        <v>16</v>
-      </c>
       <c r="X88" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y88" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="Z88" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Stadio Comunale Luigi Ferraris</t>
+          <t>Stadio Renato Dall'Ara</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Via Giovanni De Prà, 1, Genova</t>
+          <t>Via Andrea Costa, 174, Bologna</t>
         </is>
       </c>
       <c r="AC88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD88" t="n">
         <v>3</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>1</v>
       </c>
       <c r="AE88" t="n">
         <v>1.85</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG88" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AI88" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="AJ88" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AK88" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AL88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM88" t="n">
         <v>1.67</v>
       </c>
-      <c r="AM88" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AN88" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AR88" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="AS88" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
         <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1046</v>
+        <v>-1</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42785,28 +42801,28 @@
         <v>1</v>
       </c>
       <c r="BI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL88" t="n">
         <v>3</v>
       </c>
-      <c r="BJ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK88" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL88" t="n">
-        <v>2</v>
-      </c>
       <c r="BM88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ88" t="n">
         <v>2</v>
@@ -42815,7 +42831,7 @@
         <v>1</v>
       </c>
       <c r="BS88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT88" t="n">
         <v>3</v>
@@ -42824,25 +42840,25 @@
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="BW88" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BX88" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="BY88" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="CA88" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="CB88" t="n">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -42872,13 +42888,13 @@
         <v>0</v>
       </c>
       <c r="CL88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM88" t="n">
         <v>0</v>
       </c>
       <c r="CN88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -42890,19 +42906,19 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="CS88" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="CT88" t="n">
         <v>1</v>
       </c>
       <c r="CU88" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CV88" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW88" t="n">
         <v>1</v>
@@ -42911,61 +42927,61 @@
         <v>6</v>
       </c>
       <c r="CY88" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CZ88" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="DA88" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="DB88" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="DC88" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.75</v>
+        <v>1.86</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.38</v>
+        <v>0.86</v>
       </c>
       <c r="DF88" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG88" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DH88" t="n">
-        <v>0.38</v>
+        <v>1.75</v>
       </c>
       <c r="DI88" t="n">
         <v>1.38</v>
       </c>
       <c r="DJ88" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="DK88" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="DM88" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.11</v>
+        <v>3.22</v>
       </c>
       <c r="DO88" t="n">
         <v>15</v>
       </c>
       <c r="DP88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR88" t="b">
         <v>0</v>
@@ -42983,24 +42999,24 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>16.67</v>
+        <v>14.78</v>
       </c>
       <c r="DX88" t="n">
-        <v>2.47</v>
+        <v>2.76</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr"/>
@@ -43011,67 +43027,67 @@
       </c>
       <c r="ED88" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF88" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EG88" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="EI88" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EJ88" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="EK88" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL88" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM88" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EN88" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EO88" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EP88" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -43091,143 +43107,143 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
         <v>45959.82291666666</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R89" t="n">
         <v>2</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U89" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="V89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W89" t="n">
         <v>11</v>
       </c>
       <c r="X89" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y89" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="Z89" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara</t>
+          <t>Stadio Giuseppe Meazza</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Via Andrea Costa, 174, Bologna</t>
+          <t>Via Piccolomini 5, Milano</t>
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AF89" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="AG89" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI89" t="n">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="AJ89" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="AK89" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AN89" t="n">
         <v>2.05</v>
       </c>
       <c r="AO89" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AR89" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="AS89" t="n">
-        <v>2.62</v>
+        <v>3.31</v>
       </c>
       <c r="AT89" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV89" t="n">
         <v>0</v>
@@ -43236,25 +43252,25 @@
         <v>0</v>
       </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY89" t="n">
         <v>0</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA89" t="n">
         <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>-1</v>
+        <v>470</v>
       </c>
       <c r="BC89" t="n">
         <v>0</v>
       </c>
       <c r="BD89" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="BE89" t="n">
         <v>0</v>
@@ -43269,37 +43285,37 @@
         <v>1</v>
       </c>
       <c r="BI89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BO89" t="n">
         <v>0</v>
       </c>
       <c r="BP89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT89" t="n">
         <v>3</v>
@@ -43308,34 +43324,34 @@
         <v>1</v>
       </c>
       <c r="BV89" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="BW89" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BX89" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="BY89" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BZ89" t="n">
-        <v>1.27</v>
+        <v>2.48</v>
       </c>
       <c r="CA89" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="CB89" t="n">
-        <v>2.13</v>
+        <v>3.48</v>
       </c>
       <c r="CC89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD89" t="n">
         <v>0</v>
       </c>
       <c r="CE89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF89" t="n">
         <v>0</v>
@@ -43374,16 +43390,16 @@
         <v>1</v>
       </c>
       <c r="CR89" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="CS89" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CT89" t="n">
         <v>1</v>
       </c>
       <c r="CU89" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV89" t="n">
         <v>11</v>
@@ -43392,67 +43408,67 @@
         <v>1</v>
       </c>
       <c r="CX89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CY89" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ89" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="DA89" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="DB89" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="DC89" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="DF89" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DG89" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DH89" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="DI89" t="n">
-        <v>1.38</v>
+        <v>0.5</v>
       </c>
       <c r="DJ89" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="DK89" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="DL89" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="DM89" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="DN89" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="DO89" t="n">
         <v>15</v>
       </c>
       <c r="DP89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS89" t="b">
         <v>0</v>
@@ -43467,95 +43483,79 @@
         <v>0</v>
       </c>
       <c r="DW89" t="n">
-        <v>14.78</v>
+        <v>11.46</v>
       </c>
       <c r="DX89" t="n">
-        <v>2.76</v>
+        <v>1.83</v>
       </c>
       <c r="DY89" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ89" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA89" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EB89" t="inlineStr"/>
-      <c r="EC89" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="ED89" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EE89" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EF89" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EG89" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr"/>
+      <c r="ED89" t="inlineStr"/>
+      <c r="EE89" t="inlineStr"/>
+      <c r="EF89" t="inlineStr"/>
+      <c r="EG89" t="inlineStr"/>
       <c r="EH89" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="EI89" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EJ89" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="EK89" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL89" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EM89" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EN89" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO89" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EP89" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
         <v>2.71</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF93" t="n">
         <v>3</v>
@@ -45383,7 +45383,7 @@
         <v>3.02</v>
       </c>
       <c r="DO93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP93" t="b">
         <v>0</v>
@@ -48291,7 +48291,7 @@
         <v>3.13</v>
       </c>
       <c r="DO99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -49859,12 +49859,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
@@ -49880,19 +49880,19 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -49907,92 +49907,92 @@
         <v>2</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
+        <v>2</v>
+      </c>
+      <c r="U103" t="n">
+        <v>10</v>
+      </c>
+      <c r="V103" t="n">
+        <v>4</v>
+      </c>
+      <c r="W103" t="n">
+        <v>21</v>
+      </c>
+      <c r="X103" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
         <v>3</v>
       </c>
-      <c r="U103" t="n">
-        <v>11</v>
-      </c>
-      <c r="V103" t="n">
-        <v>5</v>
-      </c>
-      <c r="W103" t="n">
-        <v>10</v>
-      </c>
-      <c r="X103" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Stadio Comunale Via del Mare</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>Viale dello Stadio, Lecce</t>
-        </is>
-      </c>
-      <c r="AC103" t="n">
-        <v>1</v>
-      </c>
       <c r="AD103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AI103" t="n">
-        <v>2.71</v>
+        <v>1.9</v>
       </c>
       <c r="AJ103" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK103" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AL103" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM103" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AN103" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AO103" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR103" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="AS103" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="AT103" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AU103" t="n">
         <v>0</v>
@@ -50022,7 +50022,7 @@
         <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE103" t="n">
         <v>0</v>
@@ -50037,13 +50037,13 @@
         <v>1</v>
       </c>
       <c r="BI103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL103" t="n">
         <v>0</v>
@@ -50052,163 +50052,163 @@
         <v>5</v>
       </c>
       <c r="BN103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
         <v>4</v>
       </c>
-      <c r="BO103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR103" t="n">
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>141</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>46</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
         <v>3</v>
       </c>
-      <c r="BS103" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT103" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV103" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW103" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX103" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY103" t="n">
-        <v>117</v>
-      </c>
-      <c r="BZ103" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CA103" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="CB103" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CC103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP103" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR103" t="n">
-        <v>40</v>
-      </c>
-      <c r="CS103" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU103" t="n">
-        <v>18</v>
-      </c>
-      <c r="CV103" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW103" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX103" t="n">
+      <c r="CY103" t="n">
         <v>9</v>
       </c>
-      <c r="CY103" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ103" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="DA103" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC103" t="n">
         <v>70</v>
       </c>
-      <c r="DB103" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC103" t="n">
-        <v>50</v>
-      </c>
       <c r="DD103" t="n">
-        <v>1.13</v>
+        <v>2.14</v>
       </c>
       <c r="DE103" t="n">
         <v>0.75</v>
       </c>
       <c r="DF103" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="DG103" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DH103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DI103" t="n">
         <v>0.9</v>
       </c>
-      <c r="DI103" t="n">
-        <v>0.5</v>
-      </c>
       <c r="DJ103" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="DK103" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="DL103" t="n">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
       <c r="DM103" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="DN103" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="DO103" t="n">
         <v>15</v>
@@ -50235,87 +50235,99 @@
         <v>0</v>
       </c>
       <c r="DW103" t="n">
-        <v>19</v>
+        <v>13.12</v>
       </c>
       <c r="DX103" t="n">
-        <v>6.57</v>
+        <v>2.07</v>
       </c>
       <c r="DY103" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ103" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="EA103" t="inlineStr">
         <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="EB103" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
       <c r="EC103" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED103" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EE103" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EF103" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EG103" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EH103" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EI103" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EJ103" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EK103" t="inlineStr">
         <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EL103" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL103" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EM103" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EN103" t="inlineStr"/>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EN103" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EO103" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EP103" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -50335,12 +50347,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
@@ -50356,19 +50368,19 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -50383,92 +50395,92 @@
         <v>2</v>
       </c>
       <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3</v>
+      </c>
+      <c r="U104" t="n">
+        <v>11</v>
+      </c>
+      <c r="V104" t="n">
+        <v>5</v>
+      </c>
+      <c r="W104" t="n">
+        <v>10</v>
+      </c>
+      <c r="X104" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Stadio Comunale Via del Mare</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Viale dello Stadio, Lecce</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="n">
         <v>4</v>
       </c>
-      <c r="T104" t="n">
-        <v>2</v>
-      </c>
-      <c r="U104" t="n">
-        <v>10</v>
-      </c>
-      <c r="V104" t="n">
-        <v>4</v>
-      </c>
-      <c r="W104" t="n">
-        <v>21</v>
-      </c>
-      <c r="X104" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sinigaglia, 3, Como</t>
-        </is>
-      </c>
-      <c r="AC104" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>1</v>
-      </c>
       <c r="AE104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ104" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF104" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR104" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="AS104" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="AT104" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU104" t="n">
         <v>0</v>
@@ -50498,7 +50510,7 @@
         <v>0</v>
       </c>
       <c r="BD104" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE104" t="n">
         <v>0</v>
@@ -50513,13 +50525,13 @@
         <v>1</v>
       </c>
       <c r="BI104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL104" t="n">
         <v>0</v>
@@ -50528,49 +50540,49 @@
         <v>5</v>
       </c>
       <c r="BN104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BO104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR104" t="n">
         <v>3</v>
       </c>
-      <c r="BR104" t="n">
-        <v>1</v>
-      </c>
       <c r="BS104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU104" t="n">
         <v>1</v>
       </c>
       <c r="BV104" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BW104" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="BX104" t="n">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="BY104" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="BZ104" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="CA104" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="CB104" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="CC104" t="n">
         <v>0</v>
@@ -50618,76 +50630,76 @@
         <v>1</v>
       </c>
       <c r="CR104" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="CS104" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CT104" t="n">
         <v>1</v>
       </c>
       <c r="CU104" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CV104" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CW104" t="n">
         <v>1</v>
       </c>
       <c r="CX104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CY104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ104" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="DA104" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="DB104" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DC104" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE104" t="n">
         <v>0.75</v>
       </c>
       <c r="DF104" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG104" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DH104" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="DI104" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="DJ104" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="DK104" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="DL104" t="n">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="DM104" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="DN104" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="DO104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP104" t="b">
         <v>0</v>
@@ -50711,99 +50723,87 @@
         <v>0</v>
       </c>
       <c r="DW104" t="n">
-        <v>13.12</v>
+        <v>19</v>
       </c>
       <c r="DX104" t="n">
-        <v>2.07</v>
+        <v>6.57</v>
       </c>
       <c r="DY104" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ104" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA104" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EB104" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr"/>
       <c r="EC104" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="ED104" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EE104" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EF104" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EG104" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH104" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI104" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EJ104" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EK104" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EL104" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr"/>
       <c r="EM104" t="inlineStr">
         <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EN104" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr"/>
       <c r="EO104" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EP104" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
@@ -53514,7 +53514,7 @@
         <v>70</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE110" t="n">
         <v>1.43</v>
@@ -53547,7 +53547,7 @@
         <v>2.88</v>
       </c>
       <c r="DO110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -54131,116 +54131,116 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
         <v>45983.58333333334</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
         <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K112" t="n">
         <v>2</v>
       </c>
       <c r="L112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T112" t="n">
         <v>5</v>
       </c>
       <c r="U112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V112" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W112" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X112" t="n">
         <v>16</v>
       </c>
       <c r="Y112" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z112" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Dacia Arena</t>
+          <t>Sardegna Arena</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Piazza le Repubblica Argentina, 3, Udine</t>
+          <t>Via Raimondo Carta Raspi, Cagliari</t>
         </is>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE112" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AF112" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="AG112" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AI112" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AJ112" t="n">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="AK112" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="AL112" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AM112" t="n">
         <v>1.7</v>
@@ -54249,52 +54249,52 @@
         <v>2.42</v>
       </c>
       <c r="AO112" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AR112" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AS112" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="AT112" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB112" t="n">
-        <v>467</v>
+        <v>-1</v>
       </c>
       <c r="BC112" t="n">
         <v>0</v>
       </c>
       <c r="BD112" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BE112" t="n">
         <v>0</v>
@@ -54309,64 +54309,64 @@
         <v>1</v>
       </c>
       <c r="BI112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BJ112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM112" t="n">
         <v>5</v>
       </c>
       <c r="BN112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP112" t="n">
         <v>1</v>
       </c>
       <c r="BQ112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU112" t="n">
         <v>1</v>
       </c>
       <c r="BV112" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BW112" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BX112" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="BY112" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="BZ112" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CA112" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="CB112" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="CC112" t="n">
         <v>0</v>
@@ -54399,7 +54399,7 @@
         <v>0</v>
       </c>
       <c r="CM112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN112" t="n">
         <v>0</v>
@@ -54408,16 +54408,16 @@
         <v>0</v>
       </c>
       <c r="CP112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ112" t="n">
         <v>1</v>
       </c>
       <c r="CR112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS112" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CT112" t="n">
         <v>1</v>
@@ -54426,61 +54426,61 @@
         <v>16</v>
       </c>
       <c r="CV112" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="CW112" t="n">
         <v>1</v>
       </c>
       <c r="CX112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ112" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DA112" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB112" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DC112" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="DF112" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG112" t="n">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="DH112" t="n">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="DI112" t="n">
-        <v>1.91</v>
+        <v>0.64</v>
       </c>
       <c r="DJ112" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="DK112" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL112" t="n">
-        <v>1.46</v>
+        <v>0.99</v>
       </c>
       <c r="DM112" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="DN112" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="DO112" t="n">
         <v>15</v>
@@ -54495,26 +54495,26 @@
         <v>1</v>
       </c>
       <c r="DS112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW112" t="n">
-        <v>3.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DX112" t="n">
-        <v>4.58</v>
+        <v>13.07</v>
       </c>
       <c r="DY112" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="DZ112" t="inlineStr">
@@ -54524,78 +54524,62 @@
       </c>
       <c r="EA112" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EB112" t="inlineStr"/>
       <c r="EC112" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="ED112" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EE112" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF112" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG112" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EH112" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EI112" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ112" t="inlineStr">
         <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EK112" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EL112" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EM112" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EN112" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EK112" t="inlineStr"/>
+      <c r="EL112" t="inlineStr"/>
+      <c r="EM112" t="inlineStr"/>
+      <c r="EN112" t="inlineStr"/>
       <c r="EO112" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EP112" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
@@ -54615,116 +54599,116 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
         <v>45983.58333333334</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K113" t="n">
         <v>2</v>
       </c>
       <c r="L113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
+        <v>3</v>
+      </c>
+      <c r="R113" t="n">
         <v>5</v>
       </c>
-      <c r="R113" t="n">
-        <v>8</v>
-      </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T113" t="n">
         <v>5</v>
       </c>
       <c r="U113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V113" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W113" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="X113" t="n">
         <v>16</v>
       </c>
       <c r="Y113" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Z113" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Sardegna Arena</t>
+          <t>Dacia Arena</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Via Raimondo Carta Raspi, Cagliari</t>
+          <t>Piazza le Repubblica Argentina, 3, Udine</t>
         </is>
       </c>
       <c r="AC113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI113" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AJ113" t="n">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK113" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AL113" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AM113" t="n">
         <v>1.7</v>
@@ -54733,52 +54717,52 @@
         <v>2.42</v>
       </c>
       <c r="AO113" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AR113" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AS113" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AU113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>-1</v>
+        <v>467</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -54793,64 +54777,64 @@
         <v>1</v>
       </c>
       <c r="BI113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM113" t="n">
         <v>5</v>
       </c>
       <c r="BN113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP113" t="n">
         <v>1</v>
       </c>
       <c r="BQ113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU113" t="n">
         <v>1</v>
       </c>
       <c r="BV113" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW113" t="n">
         <v>34</v>
       </c>
-      <c r="BW113" t="n">
-        <v>35</v>
-      </c>
       <c r="BX113" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="BY113" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="BZ113" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -54883,7 +54867,7 @@
         <v>0</v>
       </c>
       <c r="CM113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN113" t="n">
         <v>0</v>
@@ -54892,16 +54876,16 @@
         <v>0</v>
       </c>
       <c r="CP113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ113" t="n">
         <v>1</v>
       </c>
       <c r="CR113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS113" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CT113" t="n">
         <v>1</v>
@@ -54910,61 +54894,61 @@
         <v>16</v>
       </c>
       <c r="CV113" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
       </c>
       <c r="CX113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY113" t="n">
         <v>7</v>
       </c>
-      <c r="CY113" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ113" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DA113" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DC113" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="DF113" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="DG113" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="DH113" t="n">
-        <v>0.91</v>
+        <v>1.36</v>
       </c>
       <c r="DI113" t="n">
-        <v>0.64</v>
+        <v>1.91</v>
       </c>
       <c r="DJ113" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="DK113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL113" t="n">
-        <v>0.99</v>
+        <v>1.46</v>
       </c>
       <c r="DM113" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="DN113" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="DO113" t="n">
         <v>15</v>
@@ -54979,26 +54963,26 @@
         <v>1</v>
       </c>
       <c r="DS113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW113" t="n">
-        <v>9.859999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="DX113" t="n">
-        <v>13.07</v>
+        <v>4.58</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
@@ -55008,62 +54992,78 @@
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr"/>
       <c r="EC113" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="ED113" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EE113" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF113" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG113" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EI113" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EJ113" t="inlineStr">
         <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EK113" t="inlineStr"/>
-      <c r="EL113" t="inlineStr"/>
-      <c r="EM113" t="inlineStr"/>
-      <c r="EN113" t="inlineStr"/>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EM113" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN113" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
       <c r="EO113" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EP113" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.79</t>
         </is>
       </c>
     </row>
@@ -56867,7 +56867,7 @@
         <v>2.61</v>
       </c>
       <c r="DO117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -58249,7 +58249,7 @@
         <v>1.38</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF120" t="n">
         <v>1.6</v>
@@ -58279,7 +58279,7 @@
         <v>2.69</v>
       </c>
       <c r="DO120" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -59247,7 +59247,7 @@
         <v>2.7</v>
       </c>
       <c r="DO122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -63050,7 +63050,7 @@
         <v>59</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE130" t="n">
         <v>1.5</v>
@@ -63083,7 +63083,7 @@
         <v>3.32</v>
       </c>
       <c r="DO130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -64465,7 +64465,7 @@
         <v>2.25</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF133" t="n">
         <v>2.14</v>
@@ -64495,7 +64495,7 @@
         <v>3.53</v>
       </c>
       <c r="DO133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -65931,7 +65931,7 @@
         <v>2.62</v>
       </c>
       <c r="DO136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -69905,10 +69905,10 @@
         <v>15</v>
       </c>
       <c r="Y145" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z145" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
@@ -70845,10 +70845,10 @@
         <v>22</v>
       </c>
       <c r="Y147" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z147" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>7</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N149" t="n">
         <v>3</v>
@@ -71829,7 +71829,7 @@
         </is>
       </c>
       <c r="AC149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD149" t="n">
         <v>3</v>
@@ -71949,7 +71949,7 @@
         <v>0</v>
       </c>
       <c r="BQ149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR149" t="n">
         <v>3</v>
@@ -71958,7 +71958,7 @@
         <v>0</v>
       </c>
       <c r="BT149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU149" t="n">
         <v>1</v>
@@ -72030,7 +72030,7 @@
         <v>1</v>
       </c>
       <c r="CR149" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS149" t="n">
         <v>23</v>
@@ -72283,13 +72283,13 @@
         <v>3</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T150" t="n">
         <v>10</v>
       </c>
       <c r="U150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V150" t="n">
         <v>13</v>
@@ -72464,13 +72464,13 @@
         <v>107</v>
       </c>
       <c r="BZ150" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="CA150" t="n">
         <v>1.34</v>
       </c>
       <c r="CB150" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CC150" t="n">
         <v>0</v>
@@ -72628,17 +72628,17 @@
       </c>
       <c r="EA150" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr">
@@ -72648,7 +72648,7 @@
       </c>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr">
@@ -72663,22 +72663,22 @@
       </c>
       <c r="EH150" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EI150" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL150" t="inlineStr">
@@ -72688,22 +72688,506 @@
       </c>
       <c r="EM150" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EN150" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EO150" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EP150" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Italy_Serie_A_2025-2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>15</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46006.82291666666</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>6</v>
+      </c>
+      <c r="K151" t="n">
+        <v>3</v>
+      </c>
+      <c r="L151" t="n">
+        <v>9</v>
+      </c>
+      <c r="M151" t="n">
+        <v>3</v>
+      </c>
+      <c r="N151" t="n">
+        <v>3</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>4</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="n">
+        <v>12</v>
+      </c>
+      <c r="U151" t="n">
+        <v>14</v>
+      </c>
+      <c r="V151" t="n">
+        <v>13</v>
+      </c>
+      <c r="W151" t="n">
+        <v>16</v>
+      </c>
+      <c r="X151" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+        </is>
+      </c>
+      <c r="AC151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>113</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY151" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ151" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA151" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB151" t="n">
+        <v>15</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DJ151" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK151" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DM151" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN151" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO151" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW151" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="DX151" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DY151" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ151" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="EA151" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EB151" t="inlineStr"/>
+      <c r="EC151" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG151" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH151" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EI151" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EJ151" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EK151" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL151" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EM151" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EN151" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EO151" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP151" t="inlineStr">
+        <is>
+          <t>1.97</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_A_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP220" headerRowCount="1">
-  <autoFilter ref="A1:EP220"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP221" headerRowCount="1">
+  <autoFilter ref="A1:EP221"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP220"/>
+  <dimension ref="A1:EP221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -10443,7 +10443,7 @@
         <v>0.96</v>
       </c>
       <c r="DO20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10901,7 +10901,7 @@
         <v>2.33</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10931,7 +10931,7 @@
         <v>2.18</v>
       </c>
       <c r="DO21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -13281,7 +13281,7 @@
         <v>0.64</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13311,7 +13311,7 @@
         <v>2</v>
       </c>
       <c r="DO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -15166,7 +15166,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE30" t="n">
         <v>1</v>
@@ -15199,7 +15199,7 @@
         <v>0.68</v>
       </c>
       <c r="DO30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP30" t="b">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE34" t="n">
         <v>1.55</v>
@@ -17111,7 +17111,7 @@
         <v>3.55</v>
       </c>
       <c r="DO34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17583,7 +17583,7 @@
         <v>3.11</v>
       </c>
       <c r="DO35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -22345,7 +22345,7 @@
         <v>1.27</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -22375,7 +22375,7 @@
         <v>2.21</v>
       </c>
       <c r="DO45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23331,7 +23331,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -25666,7 +25666,7 @@
         <v>75</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE52" t="n">
         <v>1.09</v>
@@ -25699,7 +25699,7 @@
         <v>2.95</v>
       </c>
       <c r="DO52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -28103,7 +28103,7 @@
         <v>2.62</v>
       </c>
       <c r="DO57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -30507,7 +30507,7 @@
         <v>2.2</v>
       </c>
       <c r="DO62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -34785,7 +34785,7 @@
         <v>1.1</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF71" t="n">
         <v>2</v>
@@ -34815,7 +34815,7 @@
         <v>2.22</v>
       </c>
       <c r="DO71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -36243,7 +36243,7 @@
         <v>2.66</v>
       </c>
       <c r="DO74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -38130,7 +38130,7 @@
         <v>50</v>
       </c>
       <c r="DD78" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE78" t="n">
         <v>1.08</v>
@@ -38163,7 +38163,7 @@
         <v>2.96</v>
       </c>
       <c r="DO78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -40699,12 +40699,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
@@ -40720,13 +40720,13 @@
         <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M84" t="n">
         <v>1</v>
@@ -40741,45 +40741,37 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R84" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U84" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="V84" t="n">
+        <v>8</v>
+      </c>
+      <c r="W84" t="n">
+        <v>12</v>
+      </c>
+      <c r="X84" t="n">
         <v>13</v>
       </c>
-      <c r="W84" t="n">
-        <v>11</v>
-      </c>
-      <c r="X84" t="n">
-        <v>21</v>
-      </c>
       <c r="Y84" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Z84" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sinigaglia, 3, Como</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>1</v>
       </c>
@@ -40787,52 +40779,52 @@
         <v>4</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AF84" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AG84" t="n">
-        <v>6.35</v>
+        <v>8</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI84" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AJ84" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AK84" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL84" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AM84" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="AO84" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR84" t="n">
-        <v>3.23</v>
+        <v>2.5</v>
       </c>
       <c r="AS84" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU84" t="n">
         <v>4</v>
@@ -40856,19 +40848,19 @@
         <v>2</v>
       </c>
       <c r="BB84" t="n">
-        <v>518</v>
+        <v>90</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>10167</v>
+        <v>40034</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -40877,22 +40869,22 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL84" t="n">
         <v>3</v>
-      </c>
-      <c r="BK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL84" t="n">
-        <v>0</v>
       </c>
       <c r="BM84" t="n">
         <v>4</v>
       </c>
       <c r="BN84" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO84" t="n">
         <v>0</v>
@@ -40916,258 +40908,242 @@
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="BW84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BX84" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="BY84" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="BZ84" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="CA84" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW84" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="DX84" t="n">
         <v>1.65</v>
       </c>
-      <c r="CB84" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS84" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU84" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV84" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX84" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY84" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ84" t="n">
-        <v>13</v>
-      </c>
-      <c r="DA84" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB84" t="n">
-        <v>13</v>
-      </c>
-      <c r="DC84" t="n">
-        <v>63</v>
-      </c>
-      <c r="DD84" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE84" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DF84" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG84" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH84" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DI84" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DJ84" t="n">
-        <v>88</v>
-      </c>
-      <c r="DK84" t="n">
-        <v>13</v>
-      </c>
-      <c r="DL84" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DM84" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DN84" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="DO84" t="n">
-        <v>21</v>
-      </c>
-      <c r="DP84" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ84" t="b">
-        <v>1</v>
-      </c>
-      <c r="DR84" t="b">
-        <v>1</v>
-      </c>
-      <c r="DS84" t="b">
-        <v>1</v>
-      </c>
-      <c r="DT84" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU84" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV84" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW84" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="DX84" t="n">
-        <v>1.81</v>
-      </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EC84" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="ED84" t="inlineStr">
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr"/>
+      <c r="EE84" t="inlineStr"/>
+      <c r="EF84" t="inlineStr"/>
+      <c r="EG84" t="inlineStr"/>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM84" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EO84" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="EE84" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF84" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG84" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EH84" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="EI84" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EJ84" t="inlineStr">
-        <is>
-          <t>6.94</t>
-        </is>
-      </c>
-      <c r="EK84" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EL84" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EM84" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="EN84" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EO84" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EP84" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -41187,37 +41163,37 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>45959.72916666666</v>
       </c>
       <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
         <v>3</v>
       </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" t="n">
-        <v>4</v>
-      </c>
       <c r="J85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>4</v>
@@ -41229,126 +41205,134 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S85" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U85" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="V85" t="n">
         <v>8</v>
       </c>
       <c r="W85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X85" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y85" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Z85" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+        </is>
+      </c>
       <c r="AC85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>4</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AF85" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="AG85" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AJ85" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK85" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO85" t="n">
         <v>2.05</v>
       </c>
-      <c r="AL85" t="n">
+      <c r="AP85" t="n">
         <v>1.73</v>
       </c>
-      <c r="AM85" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AQ85" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AS85" t="n">
         <v>2.9</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AU85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX85" t="n">
         <v>2</v>
       </c>
       <c r="AY85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>40034</v>
+        <v>61043</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -41363,175 +41347,175 @@
         <v>1</v>
       </c>
       <c r="BK85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BL85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM85" t="n">
         <v>4</v>
       </c>
       <c r="BN85" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV85" t="n">
         <v>8</v>
       </c>
-      <c r="BO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT85" t="n">
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
         <v>3</v>
       </c>
-      <c r="BU85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV85" t="n">
-        <v>58</v>
-      </c>
-      <c r="BW85" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX85" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY85" t="n">
-        <v>73</v>
-      </c>
-      <c r="BZ85" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CA85" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="CB85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="CC85" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE85" t="n">
-        <v>2</v>
-      </c>
-      <c r="CF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS85" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU85" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV85" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>5</v>
-      </c>
       <c r="CY85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA85" t="n">
         <v>38</v>
       </c>
-      <c r="DA85" t="n">
-        <v>75</v>
-      </c>
       <c r="DB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC85" t="n">
         <v>38</v>
       </c>
-      <c r="DC85" t="n">
-        <v>75</v>
-      </c>
       <c r="DD85" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF85" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG85" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI85" t="n">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="DJ85" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK85" t="n">
         <v>63</v>
       </c>
-      <c r="DK85" t="n">
-        <v>25</v>
-      </c>
       <c r="DL85" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="DN85" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="DO85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41543,7 +41527,7 @@
         <v>1</v>
       </c>
       <c r="DS85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT85" t="b">
         <v>0</v>
@@ -41555,83 +41539,99 @@
         <v>1</v>
       </c>
       <c r="DW85" t="n">
-        <v>11.6</v>
+        <v>19.56</v>
       </c>
       <c r="DX85" t="n">
-        <v>1.65</v>
+        <v>5.19</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="EA85" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="EB85" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EC85" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr"/>
-      <c r="EE85" t="inlineStr"/>
-      <c r="EF85" t="inlineStr"/>
-      <c r="EG85" t="inlineStr"/>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH85" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="EI85" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EJ85" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="EK85" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL85" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EM85" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EN85" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EO85" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EP85" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
@@ -41651,37 +41651,37 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>45959.72916666666</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
       </c>
       <c r="I86" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
         <v>3</v>
       </c>
-      <c r="J86" t="n">
-        <v>9</v>
-      </c>
-      <c r="K86" t="n">
-        <v>2</v>
-      </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
         <v>4</v>
@@ -41693,158 +41693,158 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U86" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V86" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X86" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Y86" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="Z86" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Stadio Olimpico</t>
+          <t>Stadio Giuseppe Sinigaglia</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD86" t="n">
         <v>4</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF86" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AG86" t="n">
-        <v>7.5</v>
+        <v>6.35</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AJ86" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AK86" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AL86" t="n">
         <v>1.7</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AN86" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AO86" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AQ86" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT86" t="n">
         <v>1.36</v>
       </c>
-      <c r="AR86" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AU86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>518</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>10167</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ86" t="n">
         <v>3</v>
       </c>
-      <c r="AV86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX86" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ86" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB86" t="n">
-        <v>113</v>
-      </c>
-      <c r="BC86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF86" t="n">
-        <v>61043</v>
-      </c>
-      <c r="BG86" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH86" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI86" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ86" t="n">
-        <v>1</v>
-      </c>
       <c r="BK86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM86" t="n">
         <v>4</v>
       </c>
       <c r="BN86" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BO86" t="n">
         <v>0</v>
@@ -41853,7 +41853,7 @@
         <v>2</v>
       </c>
       <c r="BQ86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR86" t="n">
         <v>2</v>
@@ -41862,31 +41862,31 @@
         <v>2</v>
       </c>
       <c r="BT86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU86" t="n">
         <v>1</v>
       </c>
       <c r="BV86" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="BW86" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BX86" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="BY86" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="BZ86" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="CA86" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="CB86" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="CC86" t="n">
         <v>0</v>
@@ -41913,13 +41913,13 @@
         <v>1</v>
       </c>
       <c r="CK86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL86" t="n">
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN86" t="n">
         <v>0</v>
@@ -41934,19 +41934,19 @@
         <v>1</v>
       </c>
       <c r="CR86" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CS86" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="CT86" t="n">
         <v>1</v>
       </c>
       <c r="CU86" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="CV86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW86" t="n">
         <v>1</v>
@@ -41958,49 +41958,49 @@
         <v>9</v>
       </c>
       <c r="CZ86" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DA86" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="DB86" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DC86" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DD86" t="n">
         <v>2</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.18</v>
+        <v>0.73</v>
       </c>
       <c r="DF86" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG86" t="n">
         <v>0.5</v>
       </c>
       <c r="DH86" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="DI86" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="DJ86" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DK86" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="DL86" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="DN86" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DO86" t="n">
         <v>22</v>
@@ -42015,7 +42015,7 @@
         <v>1</v>
       </c>
       <c r="DS86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT86" t="b">
         <v>0</v>
@@ -42027,99 +42027,99 @@
         <v>1</v>
       </c>
       <c r="DW86" t="n">
-        <v>19.56</v>
+        <v>11.27</v>
       </c>
       <c r="DX86" t="n">
-        <v>5.19</v>
+        <v>1.81</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="ED86" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EE86" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF86" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG86" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EH86" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="EK86" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL86" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EM86" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="EN86" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EO86" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EP86" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -42139,176 +42139,176 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45959.82291666666</v>
       </c>
       <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
         <v>3</v>
       </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
         <v>3</v>
       </c>
-      <c r="J87" t="n">
-        <v>8</v>
-      </c>
-      <c r="K87" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>4</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="n">
+        <v>7</v>
+      </c>
+      <c r="U87" t="n">
+        <v>16</v>
+      </c>
+      <c r="V87" t="n">
+        <v>11</v>
+      </c>
+      <c r="W87" t="n">
+        <v>16</v>
+      </c>
+      <c r="X87" t="n">
         <v>13</v>
       </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>8</v>
-      </c>
-      <c r="R87" t="n">
-        <v>2</v>
-      </c>
-      <c r="S87" t="n">
-        <v>14</v>
-      </c>
-      <c r="T87" t="n">
-        <v>8</v>
-      </c>
-      <c r="U87" t="n">
-        <v>22</v>
-      </c>
-      <c r="V87" t="n">
-        <v>10</v>
-      </c>
-      <c r="W87" t="n">
-        <v>11</v>
-      </c>
-      <c r="X87" t="n">
-        <v>16</v>
-      </c>
       <c r="Y87" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza</t>
+          <t>Stadio Comunale Luigi Ferraris</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Via Piccolomini 5, Milano</t>
+          <t>Via Giovanni De Prà, 1, Genova</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.55</v>
+        <v>3.25</v>
       </c>
       <c r="AG87" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.71</v>
+        <v>2.47</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AN87" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AO87" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.45</v>
+        <v>3.27</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB87" t="n">
-        <v>470</v>
+        <v>1046</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>71096</v>
+        <v>30083</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -42320,34 +42320,34 @@
         <v>3</v>
       </c>
       <c r="BJ87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL87" t="n">
         <v>2</v>
       </c>
       <c r="BM87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN87" t="n">
         <v>6</v>
       </c>
-      <c r="BN87" t="n">
-        <v>7</v>
-      </c>
       <c r="BO87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP87" t="n">
         <v>0</v>
       </c>
       <c r="BQ87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>3</v>
@@ -42356,34 +42356,34 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BW87" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BX87" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="BY87" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="BZ87" t="n">
-        <v>2.48</v>
+        <v>1.48</v>
       </c>
       <c r="CA87" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.48</v>
+        <v>2.64</v>
       </c>
       <c r="CC87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD87" t="n">
         <v>0</v>
       </c>
       <c r="CE87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF87" t="n">
         <v>0</v>
@@ -42404,13 +42404,13 @@
         <v>0</v>
       </c>
       <c r="CL87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM87" t="n">
         <v>0</v>
       </c>
       <c r="CN87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO87" t="n">
         <v>0</v>
@@ -42422,34 +42422,34 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV87" t="n">
         <v>16</v>
       </c>
-      <c r="CS87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>11</v>
-      </c>
       <c r="CW87" t="n">
         <v>1</v>
       </c>
       <c r="CX87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CZ87" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="DA87" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB87" t="n">
         <v>38</v>
@@ -42458,37 +42458,37 @@
         <v>50</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.33</v>
+        <v>1.08</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="DF87" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="DG87" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="DH87" t="n">
-        <v>1.88</v>
+        <v>0.38</v>
       </c>
       <c r="DI87" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="DJ87" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DK87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL87" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.25</v>
+        <v>2.11</v>
       </c>
       <c r="DO87" t="n">
         <v>22</v>
@@ -42500,7 +42500,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42515,79 +42515,95 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>11.46</v>
+        <v>16.67</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EB87" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EC87" t="inlineStr"/>
-      <c r="ED87" t="inlineStr"/>
-      <c r="EE87" t="inlineStr"/>
-      <c r="EF87" t="inlineStr"/>
-      <c r="EG87" t="inlineStr"/>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr"/>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EI87" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EJ87" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="EK87" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EM87" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EN87" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EO87" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP87" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -42607,176 +42623,176 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45959.82291666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>13</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>8</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2</v>
+      </c>
+      <c r="S88" t="n">
+        <v>14</v>
+      </c>
+      <c r="T88" t="n">
+        <v>8</v>
+      </c>
+      <c r="U88" t="n">
+        <v>22</v>
+      </c>
+      <c r="V88" t="n">
+        <v>10</v>
+      </c>
+      <c r="W88" t="n">
+        <v>11</v>
+      </c>
+      <c r="X88" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Via Piccolomini 5, Milano</t>
+        </is>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU88" t="n">
         <v>3</v>
       </c>
-      <c r="L88" t="n">
-        <v>10</v>
-      </c>
-      <c r="M88" t="n">
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
         <v>3</v>
       </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>4</v>
-      </c>
-      <c r="S88" t="n">
-        <v>15</v>
-      </c>
-      <c r="T88" t="n">
-        <v>7</v>
-      </c>
-      <c r="U88" t="n">
-        <v>16</v>
-      </c>
-      <c r="V88" t="n">
-        <v>11</v>
-      </c>
-      <c r="W88" t="n">
-        <v>16</v>
-      </c>
-      <c r="X88" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Stadio Comunale Luigi Ferraris</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>Via Giovanni De Prà, 1, Genova</t>
-        </is>
-      </c>
-      <c r="AC88" t="n">
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
         <v>3</v>
       </c>
-      <c r="AD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK88" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL88" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM88" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO88" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ88" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR88" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AS88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT88" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU88" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>1</v>
-      </c>
       <c r="BA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1046</v>
+        <v>470</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>30083</v>
+        <v>71096</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>
@@ -42788,34 +42804,34 @@
         <v>3</v>
       </c>
       <c r="BJ88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL88" t="n">
         <v>2</v>
       </c>
       <c r="BM88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP88" t="n">
         <v>0</v>
       </c>
       <c r="BQ88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT88" t="n">
         <v>3</v>
@@ -42824,34 +42840,34 @@
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="BW88" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BX88" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="BY88" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="CA88" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="CB88" t="n">
-        <v>2.64</v>
+        <v>3.48</v>
       </c>
       <c r="CC88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD88" t="n">
         <v>0</v>
       </c>
       <c r="CE88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF88" t="n">
         <v>0</v>
@@ -42872,13 +42888,13 @@
         <v>0</v>
       </c>
       <c r="CL88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM88" t="n">
         <v>0</v>
       </c>
       <c r="CN88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -42890,34 +42906,34 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="CS88" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="CT88" t="n">
         <v>1</v>
       </c>
       <c r="CU88" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CV88" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW88" t="n">
         <v>1</v>
       </c>
       <c r="CX88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CY88" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CZ88" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DA88" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB88" t="n">
         <v>38</v>
@@ -42926,37 +42942,37 @@
         <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.08</v>
+        <v>2.33</v>
       </c>
       <c r="DE88" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="DF88" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI88" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG88" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH88" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DI88" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DJ88" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="DK88" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="DM88" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.11</v>
+        <v>3.25</v>
       </c>
       <c r="DO88" t="n">
         <v>22</v>
@@ -42968,7 +42984,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -42983,95 +42999,79 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>16.67</v>
+        <v>11.46</v>
       </c>
       <c r="DX88" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="EB88" t="inlineStr"/>
-      <c r="EC88" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr"/>
+      <c r="ED88" t="inlineStr"/>
+      <c r="EE88" t="inlineStr"/>
+      <c r="EF88" t="inlineStr"/>
+      <c r="EG88" t="inlineStr"/>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>8.65</t>
+        </is>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EP88" t="inlineStr">
         <is>
           <t>2.01</t>
-        </is>
-      </c>
-      <c r="EE88" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EG88" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EH88" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="EI88" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr">
-        <is>
-          <t>5.48</t>
-        </is>
-      </c>
-      <c r="EK88" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EL88" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="EN88" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="EO88" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EP88" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -44895,7 +44895,7 @@
         <v>2.87</v>
       </c>
       <c r="DO92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -46322,7 +46322,7 @@
         <v>75</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE95" t="n">
         <v>2.4</v>
@@ -46355,7 +46355,7 @@
         <v>3.41</v>
       </c>
       <c r="DO95" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -50211,7 +50211,7 @@
         <v>2.44</v>
       </c>
       <c r="DO103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP103" t="b">
         <v>0</v>
@@ -53517,7 +53517,7 @@
         <v>2</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF110" t="n">
         <v>1.8</v>
@@ -53547,7 +53547,7 @@
         <v>2.88</v>
       </c>
       <c r="DO110" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -54483,7 +54483,7 @@
         <v>2.68</v>
       </c>
       <c r="DO112" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -56374,7 +56374,7 @@
         <v>40</v>
       </c>
       <c r="DD116" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE116" t="n">
         <v>1.18</v>
@@ -56407,7 +56407,7 @@
         <v>2.67</v>
       </c>
       <c r="DO116" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -59697,7 +59697,7 @@
         <v>0.91</v>
       </c>
       <c r="DE123" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF123" t="n">
         <v>1</v>
@@ -59727,7 +59727,7 @@
         <v>2.2</v>
       </c>
       <c r="DO123" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -60211,7 +60211,7 @@
         <v>2.66</v>
       </c>
       <c r="DO124" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -64934,7 +64934,7 @@
         <v>67</v>
       </c>
       <c r="DD134" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE134" t="n">
         <v>1.3</v>
@@ -64967,7 +64967,7 @@
         <v>2.75</v>
       </c>
       <c r="DO134" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -67827,7 +67827,7 @@
         <v>2.67</v>
       </c>
       <c r="DO140" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -71131,7 +71131,7 @@
         <v>2.64</v>
       </c>
       <c r="DO147" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -71615,7 +71615,7 @@
         <v>3.09</v>
       </c>
       <c r="DO148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -75413,7 +75413,7 @@
         <v>0.82</v>
       </c>
       <c r="DE156" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF156" t="n">
         <v>0.29</v>
@@ -75443,7 +75443,7 @@
         <v>2.65</v>
       </c>
       <c r="DO156" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -77835,7 +77835,7 @@
         <v>2.69</v>
       </c>
       <c r="DO161" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -78791,7 +78791,7 @@
         <v>2.94</v>
       </c>
       <c r="DO163" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -81653,7 +81653,7 @@
         <v>2</v>
       </c>
       <c r="DE169" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF169" t="n">
         <v>2.14</v>
@@ -81683,7 +81683,7 @@
         <v>2.86</v>
       </c>
       <c r="DO169" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -81803,12 +81803,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
@@ -81824,119 +81824,119 @@
         <v>2</v>
       </c>
       <c r="J170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K170" t="n">
         <v>7</v>
       </c>
       <c r="L170" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
         <v>3</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>4</v>
-      </c>
       <c r="R170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S170" t="n">
         <v>8</v>
       </c>
       <c r="T170" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U170" t="n">
+        <v>11</v>
+      </c>
+      <c r="V170" t="n">
+        <v>16</v>
+      </c>
+      <c r="W170" t="n">
         <v>12</v>
       </c>
-      <c r="V170" t="n">
-        <v>10</v>
-      </c>
-      <c r="W170" t="n">
-        <v>9</v>
-      </c>
       <c r="X170" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Y170" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="Z170" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>Stadio Comunale Luigi Ferraris</t>
+          <t>MAPEI Stadium - Città del Tricolore</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>Via Giovanni De Prà, 1, Genova</t>
+          <t>Piazza Azzuri d'Italia, 1, Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="AC170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR170" t="n">
         <v>3</v>
       </c>
-      <c r="AE170" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF170" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG170" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI170" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AJ170" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AK170" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AL170" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM170" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AN170" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO170" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AP170" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AQ170" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR170" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AS170" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AT170" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AU170" t="n">
         <v>2</v>
@@ -81966,13 +81966,13 @@
         <v>0</v>
       </c>
       <c r="BD170" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="BE170" t="n">
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>31661</v>
+        <v>12701</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -81984,61 +81984,61 @@
         <v>2</v>
       </c>
       <c r="BJ170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN170" t="n">
         <v>4</v>
       </c>
-      <c r="BK170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL170" t="n">
+      <c r="BO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT170" t="n">
         <v>3</v>
       </c>
-      <c r="BM170" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN170" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT170" t="n">
-        <v>2</v>
-      </c>
       <c r="BU170" t="n">
         <v>1</v>
       </c>
       <c r="BV170" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="BW170" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="BX170" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="BY170" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="BZ170" t="n">
         <v>1.4</v>
       </c>
       <c r="CA170" t="n">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="CB170" t="n">
-        <v>2.56</v>
+        <v>3.07</v>
       </c>
       <c r="CC170" t="n">
         <v>0</v>
@@ -82071,10 +82071,10 @@
         <v>0</v>
       </c>
       <c r="CM170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO170" t="n">
         <v>0</v>
@@ -82086,73 +82086,73 @@
         <v>1</v>
       </c>
       <c r="CR170" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CS170" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT170" t="n">
         <v>1</v>
       </c>
       <c r="CU170" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="CV170" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CW170" t="n">
         <v>1</v>
       </c>
       <c r="CX170" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CY170" t="n">
         <v>10</v>
       </c>
       <c r="CZ170" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA170" t="n">
         <v>60</v>
       </c>
-      <c r="DA170" t="n">
-        <v>72</v>
-      </c>
       <c r="DB170" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC170" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD170" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE170" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG170" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ170" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK170" t="n">
         <v>41</v>
       </c>
-      <c r="DC170" t="n">
-        <v>72</v>
-      </c>
-      <c r="DD170" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="DE170" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DF170" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DG170" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DH170" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DI170" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="DJ170" t="n">
-        <v>41</v>
-      </c>
-      <c r="DK170" t="n">
-        <v>29</v>
-      </c>
       <c r="DL170" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DM170" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="DN170" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="DO170" t="n">
         <v>22</v>
@@ -82179,71 +82179,99 @@
         <v>1</v>
       </c>
       <c r="DW170" t="n">
-        <v>8.31</v>
+        <v>4.64</v>
       </c>
       <c r="DX170" t="n">
-        <v>4.49</v>
+        <v>1.08</v>
       </c>
       <c r="DY170" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ170" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="EA170" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EB170" t="inlineStr"/>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EB170" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
       <c r="EC170" t="inlineStr">
         <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="ED170" t="inlineStr"/>
-      <c r="EE170" t="inlineStr"/>
-      <c r="EF170" t="inlineStr"/>
-      <c r="EG170" t="inlineStr"/>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED170" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EE170" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EF170" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EG170" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
       <c r="EH170" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EI170" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EJ170" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="EK170" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EL170" t="inlineStr"/>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EL170" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
       <c r="EM170" t="inlineStr">
         <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EN170" t="inlineStr"/>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EN170" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
       <c r="EO170" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP170" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -82263,12 +82291,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F171" s="2" t="n">
@@ -82284,19 +82312,19 @@
         <v>2</v>
       </c>
       <c r="J171" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K171" t="n">
         <v>7</v>
       </c>
       <c r="L171" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -82305,98 +82333,98 @@
         <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S171" t="n">
         <v>8</v>
       </c>
       <c r="T171" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U171" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V171" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="W171" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X171" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y171" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z171" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>MAPEI Stadium - Città del Tricolore</t>
+          <t>Stadio Comunale Luigi Ferraris</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>Piazza Azzuri d'Italia, 1, Reggio nell'Emilia</t>
+          <t>Via Giovanni De Prà, 1, Genova</t>
         </is>
       </c>
       <c r="AC171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO171" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF171" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG171" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH171" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI171" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AJ171" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AK171" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL171" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM171" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN171" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AO171" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AP171" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AR171" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AS171" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AT171" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU171" t="n">
         <v>2</v>
@@ -82426,13 +82454,13 @@
         <v>0</v>
       </c>
       <c r="BD171" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="BE171" t="n">
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>12701</v>
+        <v>31661</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -82444,61 +82472,61 @@
         <v>2</v>
       </c>
       <c r="BJ171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BK171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU171" t="n">
         <v>1</v>
       </c>
       <c r="BV171" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="BW171" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BX171" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="BY171" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="BZ171" t="n">
         <v>1.4</v>
       </c>
       <c r="CA171" t="n">
-        <v>1.67</v>
+        <v>1.16</v>
       </c>
       <c r="CB171" t="n">
-        <v>3.07</v>
+        <v>2.56</v>
       </c>
       <c r="CC171" t="n">
         <v>0</v>
@@ -82531,10 +82559,10 @@
         <v>0</v>
       </c>
       <c r="CM171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO171" t="n">
         <v>0</v>
@@ -82546,73 +82574,73 @@
         <v>1</v>
       </c>
       <c r="CR171" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CS171" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU171" t="n">
         <v>17</v>
       </c>
-      <c r="CT171" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU171" t="n">
-        <v>7</v>
-      </c>
       <c r="CV171" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CW171" t="n">
         <v>1</v>
       </c>
       <c r="CX171" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CY171" t="n">
         <v>10</v>
       </c>
       <c r="CZ171" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="DA171" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="DB171" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="DC171" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="DD171" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="DE171" t="n">
-        <v>1.18</v>
+        <v>0.64</v>
       </c>
       <c r="DF171" t="n">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="DG171" t="n">
-        <v>1.14</v>
+        <v>0.63</v>
       </c>
       <c r="DH171" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI171" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DJ171" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK171" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL171" t="n">
         <v>1.29</v>
       </c>
-      <c r="DI171" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="DJ171" t="n">
-        <v>61</v>
-      </c>
-      <c r="DK171" t="n">
-        <v>41</v>
-      </c>
-      <c r="DL171" t="n">
-        <v>1.28</v>
-      </c>
       <c r="DM171" t="n">
-        <v>1.16</v>
+        <v>0.98</v>
       </c>
       <c r="DN171" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="DO171" t="n">
         <v>22</v>
@@ -82639,99 +82667,71 @@
         <v>1</v>
       </c>
       <c r="DW171" t="n">
-        <v>4.64</v>
+        <v>8.31</v>
       </c>
       <c r="DX171" t="n">
-        <v>1.08</v>
+        <v>4.49</v>
       </c>
       <c r="DY171" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="DZ171" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="EA171" t="inlineStr">
         <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EB171" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EB171" t="inlineStr"/>
       <c r="EC171" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="ED171" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EE171" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EF171" t="inlineStr">
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED171" t="inlineStr"/>
+      <c r="EE171" t="inlineStr"/>
+      <c r="EF171" t="inlineStr"/>
+      <c r="EG171" t="inlineStr"/>
+      <c r="EH171" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EI171" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ171" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EK171" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL171" t="inlineStr"/>
+      <c r="EM171" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EN171" t="inlineStr"/>
+      <c r="EO171" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EP171" t="inlineStr">
         <is>
           <t>1.71</t>
-        </is>
-      </c>
-      <c r="EG171" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EH171" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="EI171" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EJ171" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="EK171" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EL171" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EM171" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="EN171" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="EO171" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EP171" t="inlineStr">
-        <is>
-          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -84978,7 +84978,7 @@
         <v>61</v>
       </c>
       <c r="DD176" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE176" t="n">
         <v>1.09</v>
@@ -85011,7 +85011,7 @@
         <v>2.77</v>
       </c>
       <c r="DO176" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP176" t="b">
         <v>1</v>
@@ -87055,40 +87055,40 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F181" s="2" t="n">
         <v>46029.72916666666</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H181" t="n">
         <v>2</v>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J181" t="n">
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -87097,212 +87097,212 @@
         <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S181" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U181" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V181" t="n">
         <v>11</v>
       </c>
       <c r="W181" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X181" t="n">
         <v>15</v>
       </c>
       <c r="Y181" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="Z181" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara</t>
+          <t>Stadio San Paolo</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>Via Andrea Costa, 174, Bologna</t>
+          <t>Pizzale Vincenzo Tecchio, Napoli</t>
         </is>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
       </c>
       <c r="AD181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE181" t="n">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="AF181" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AG181" t="n">
-        <v>2.23</v>
+        <v>11.64</v>
       </c>
       <c r="AH181" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI181" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AJ181" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AK181" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="AL181" t="n">
-        <v>2.09</v>
+        <v>1.45</v>
       </c>
       <c r="AM181" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AN181" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO181" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR181" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AS181" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AT181" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AU181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
         <v>0</v>
       </c>
       <c r="AW181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB181" t="n">
-        <v>464</v>
+        <v>-1</v>
       </c>
       <c r="BC181" t="n">
         <v>0</v>
       </c>
       <c r="BD181" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="BE181" t="n">
         <v>0</v>
       </c>
       <c r="BF181" t="n">
-        <v>23454</v>
+        <v>35000</v>
       </c>
       <c r="BG181" t="n">
         <v>2</v>
       </c>
       <c r="BH181" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ181" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BK181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BL181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM181" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BN181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO181" t="n">
         <v>0</v>
       </c>
       <c r="BP181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ181" t="n">
         <v>0</v>
       </c>
       <c r="BR181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BU181" t="n">
         <v>1</v>
       </c>
       <c r="BV181" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="BW181" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="BX181" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="BY181" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="BZ181" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="CA181" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="CB181" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC181" t="n">
         <v>0</v>
       </c>
       <c r="CD181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE181" t="n">
         <v>0</v>
       </c>
       <c r="CF181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG181" t="n">
         <v>0</v>
@@ -87323,25 +87323,25 @@
         <v>0</v>
       </c>
       <c r="CM181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN181" t="n">
         <v>0</v>
       </c>
       <c r="CO181" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP181" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ181" t="n">
         <v>1</v>
       </c>
       <c r="CR181" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="CS181" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="CT181" t="n">
         <v>1</v>
@@ -87350,61 +87350,61 @@
         <v>15</v>
       </c>
       <c r="CV181" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CW181" t="n">
         <v>1</v>
       </c>
       <c r="CX181" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CY181" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="CZ181" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="DA181" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC181" t="n">
         <v>69</v>
       </c>
-      <c r="DB181" t="n">
-        <v>32</v>
-      </c>
-      <c r="DC181" t="n">
-        <v>44</v>
-      </c>
       <c r="DD181" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="DE181" t="n">
-        <v>1.3</v>
+        <v>0.73</v>
       </c>
       <c r="DF181" t="n">
-        <v>1.75</v>
+        <v>2.71</v>
       </c>
       <c r="DG181" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="DH181" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="DI181" t="n">
-        <v>1.39</v>
+        <v>0.71</v>
       </c>
       <c r="DJ181" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="DK181" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="DL181" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="DM181" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="DN181" t="n">
-        <v>3.09</v>
+        <v>2.76</v>
       </c>
       <c r="DO181" t="n">
         <v>22</v>
@@ -87416,10 +87416,10 @@
         <v>1</v>
       </c>
       <c r="DR181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT181" t="b">
         <v>0</v>
@@ -87428,17 +87428,17 @@
         <v>0</v>
       </c>
       <c r="DV181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW181" t="n">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="DX181" t="n">
-        <v>2.56</v>
+        <v>7.04</v>
       </c>
       <c r="DY181" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="DZ181" t="inlineStr">
@@ -87448,82 +87448,66 @@
       </c>
       <c r="EA181" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB181" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EC181" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED181" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE181" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF181" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG181" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EH181" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="EI181" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="ED181" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE181" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EF181" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG181" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EH181" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="EI181" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
       <c r="EJ181" t="inlineStr">
         <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="EK181" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EL181" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EM181" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="EN181" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="EK181" t="inlineStr"/>
+      <c r="EL181" t="inlineStr"/>
+      <c r="EM181" t="inlineStr"/>
+      <c r="EN181" t="inlineStr"/>
       <c r="EO181" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EP181" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -87543,40 +87527,40 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F182" s="2" t="n">
         <v>46029.72916666666</v>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>2</v>
       </c>
       <c r="I182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L182" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -87585,212 +87569,212 @@
         <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S182" t="n">
+        <v>9</v>
+      </c>
+      <c r="T182" t="n">
+        <v>6</v>
+      </c>
+      <c r="U182" t="n">
         <v>11</v>
-      </c>
-      <c r="T182" t="n">
-        <v>7</v>
-      </c>
-      <c r="U182" t="n">
-        <v>15</v>
       </c>
       <c r="V182" t="n">
         <v>11</v>
       </c>
       <c r="W182" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X182" t="n">
         <v>15</v>
       </c>
       <c r="Y182" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="Z182" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>Stadio San Paolo</t>
+          <t>Stadio Renato Dall'Ara</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>Pizzale Vincenzo Tecchio, Napoli</t>
+          <t>Via Andrea Costa, 174, Bologna</t>
         </is>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
       </c>
       <c r="AD182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AF182" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AG182" t="n">
-        <v>11.64</v>
+        <v>2.23</v>
       </c>
       <c r="AH182" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI182" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AJ182" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="AK182" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="AL182" t="n">
-        <v>1.45</v>
+        <v>2.09</v>
       </c>
       <c r="AM182" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AN182" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AO182" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR182" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AS182" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AT182" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AU182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV182" t="n">
         <v>0</v>
       </c>
       <c r="AW182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB182" t="n">
+        <v>464</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>23454</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH182" t="n">
         <v>-1</v>
       </c>
-      <c r="BC182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD182" t="n">
-        <v>58</v>
-      </c>
-      <c r="BE182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF182" t="n">
-        <v>35000</v>
-      </c>
-      <c r="BG182" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH182" t="n">
-        <v>1</v>
-      </c>
       <c r="BI182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ182" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BK182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BL182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM182" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BN182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO182" t="n">
         <v>0</v>
       </c>
       <c r="BP182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ182" t="n">
         <v>0</v>
       </c>
       <c r="BR182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU182" t="n">
         <v>1</v>
       </c>
       <c r="BV182" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="BW182" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BX182" t="n">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="BY182" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="BZ182" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="CA182" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="CB182" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC182" t="n">
         <v>0</v>
       </c>
       <c r="CD182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE182" t="n">
         <v>0</v>
       </c>
       <c r="CF182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG182" t="n">
         <v>0</v>
@@ -87811,25 +87795,25 @@
         <v>0</v>
       </c>
       <c r="CM182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN182" t="n">
         <v>0</v>
       </c>
       <c r="CO182" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP182" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ182" t="n">
         <v>1</v>
       </c>
       <c r="CR182" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CS182" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="CT182" t="n">
         <v>1</v>
@@ -87838,95 +87822,95 @@
         <v>15</v>
       </c>
       <c r="CV182" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="CW182" t="n">
         <v>1</v>
       </c>
       <c r="CX182" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CY182" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CZ182" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="DA182" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="DB182" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="DC182" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="DD182" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE182" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF182" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG182" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH182" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DI182" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DJ182" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK182" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL182" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM182" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN182" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DO182" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP182" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ182" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW182" t="n">
         <v>2.4</v>
       </c>
-      <c r="DE182" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DF182" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="DG182" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DH182" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DI182" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DJ182" t="n">
-        <v>37</v>
-      </c>
-      <c r="DK182" t="n">
-        <v>26</v>
-      </c>
-      <c r="DL182" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DM182" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DN182" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="DO182" t="n">
-        <v>21</v>
-      </c>
-      <c r="DP182" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ182" t="b">
-        <v>1</v>
-      </c>
-      <c r="DR182" t="b">
-        <v>1</v>
-      </c>
-      <c r="DS182" t="b">
-        <v>1</v>
-      </c>
-      <c r="DT182" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU182" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV182" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW182" t="n">
-        <v>9.6</v>
-      </c>
       <c r="DX182" t="n">
-        <v>7.04</v>
+        <v>2.56</v>
       </c>
       <c r="DY182" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ182" t="inlineStr">
@@ -87936,66 +87920,82 @@
       </c>
       <c r="EA182" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EB182" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="EC182" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="ED182" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EE182" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EF182" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG182" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EH182" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EI182" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EJ182" t="inlineStr">
         <is>
-          <t>12.30</t>
-        </is>
-      </c>
-      <c r="EK182" t="inlineStr"/>
-      <c r="EL182" t="inlineStr"/>
-      <c r="EM182" t="inlineStr"/>
-      <c r="EN182" t="inlineStr"/>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EK182" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL182" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EM182" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EN182" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
       <c r="EO182" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EP182" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -88015,246 +88015,254 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F183" s="2" t="n">
         <v>46029.82291666666</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H183" t="n">
         <v>2</v>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J183" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K183" t="n">
+        <v>2</v>
+      </c>
+      <c r="L183" t="n">
+        <v>10</v>
+      </c>
+      <c r="M183" t="n">
         <v>3</v>
       </c>
-      <c r="L183" t="n">
+      <c r="N183" t="n">
+        <v>5</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>9</v>
+      </c>
+      <c r="R183" t="n">
+        <v>5</v>
+      </c>
+      <c r="S183" t="n">
+        <v>8</v>
+      </c>
+      <c r="T183" t="n">
+        <v>3</v>
+      </c>
+      <c r="U183" t="n">
+        <v>17</v>
+      </c>
+      <c r="V183" t="n">
+        <v>8</v>
+      </c>
+      <c r="W183" t="n">
+        <v>11</v>
+      </c>
+      <c r="X183" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
+        </is>
+      </c>
+      <c r="AC183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU183" t="n">
         <v>4</v>
       </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>35000</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN183" t="n">
         <v>3</v>
       </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>8</v>
-      </c>
-      <c r="S183" t="n">
-        <v>4</v>
-      </c>
-      <c r="T183" t="n">
-        <v>18</v>
-      </c>
-      <c r="U183" t="n">
-        <v>4</v>
-      </c>
-      <c r="V183" t="n">
-        <v>26</v>
-      </c>
-      <c r="W183" t="n">
-        <v>4</v>
-      </c>
-      <c r="X183" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y183" t="n">
-        <v>37</v>
-      </c>
-      <c r="Z183" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA183" t="inlineStr"/>
-      <c r="AB183" t="inlineStr"/>
-      <c r="AC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD183" t="n">
+      <c r="BO183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR183" t="n">
         <v>3</v>
       </c>
-      <c r="AE183" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF183" t="n">
+      <c r="BS183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT183" t="n">
         <v>5</v>
       </c>
-      <c r="AG183" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH183" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI183" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AK183" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL183" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM183" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN183" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO183" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AP183" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AQ183" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR183" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS183" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AT183" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AU183" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW183" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY183" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB183" t="n">
-        <v>470</v>
-      </c>
-      <c r="BC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD183" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF183" t="n">
-        <v>21601</v>
-      </c>
-      <c r="BG183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT183" t="n">
-        <v>2</v>
-      </c>
       <c r="BU183" t="n">
         <v>1</v>
       </c>
       <c r="BV183" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="BW183" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="BX183" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="BY183" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="BZ183" t="n">
-        <v>0.47</v>
+        <v>2.06</v>
       </c>
       <c r="CA183" t="n">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="CB183" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="CC183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG183" t="n">
         <v>0</v>
@@ -88275,7 +88283,7 @@
         <v>0</v>
       </c>
       <c r="CM183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN183" t="n">
         <v>0</v>
@@ -88290,73 +88298,73 @@
         <v>1</v>
       </c>
       <c r="CR183" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CS183" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CT183" t="n">
         <v>1</v>
       </c>
       <c r="CU183" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CV183" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CW183" t="n">
         <v>1</v>
       </c>
       <c r="CX183" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CY183" t="n">
         <v>5</v>
       </c>
       <c r="CZ183" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="DA183" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="DB183" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DC183" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="DD183" t="n">
-        <v>0.91</v>
+        <v>1.45</v>
       </c>
       <c r="DE183" t="n">
-        <v>2.4</v>
+        <v>0.73</v>
       </c>
       <c r="DF183" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG183" t="n">
-        <v>2.25</v>
+        <v>0.44</v>
       </c>
       <c r="DH183" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="DI183" t="n">
-        <v>2.29</v>
+        <v>0.67</v>
       </c>
       <c r="DJ183" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DK183" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="DL183" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DM183" t="n">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="DN183" t="n">
-        <v>3.01</v>
+        <v>2.52</v>
       </c>
       <c r="DO183" t="n">
         <v>22</v>
@@ -88368,10 +88376,10 @@
         <v>1</v>
       </c>
       <c r="DR183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT183" t="b">
         <v>0</v>
@@ -88380,74 +88388,98 @@
         <v>0</v>
       </c>
       <c r="DV183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW183" t="n">
-        <v>3.11</v>
+        <v>4.73</v>
       </c>
       <c r="DX183" t="n">
-        <v>2.06</v>
+        <v>5.21</v>
       </c>
       <c r="DY183" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="DZ183" t="inlineStr">
         <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="EA183" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA183" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
       <c r="EB183" t="inlineStr"/>
-      <c r="EC183" t="inlineStr"/>
+      <c r="EC183" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
       <c r="ED183" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EE183" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EF183" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EG183" t="inlineStr">
+        <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="EG183" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="EH183" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EI183" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EJ183" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EK183" t="inlineStr"/>
-      <c r="EL183" t="inlineStr"/>
-      <c r="EM183" t="inlineStr"/>
-      <c r="EN183" t="inlineStr"/>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EK183" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL183" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EM183" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EN183" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
       <c r="EO183" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EP183" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -88467,356 +88499,348 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F184" s="2" t="n">
         <v>46029.82291666666</v>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>2</v>
       </c>
       <c r="I184" t="n">
+        <v>2</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="n">
+        <v>3</v>
+      </c>
+      <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="J184" t="n">
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>3</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
         <v>8</v>
       </c>
-      <c r="K184" t="n">
-        <v>2</v>
-      </c>
-      <c r="L184" t="n">
-        <v>10</v>
-      </c>
-      <c r="M184" t="n">
+      <c r="S184" t="n">
+        <v>4</v>
+      </c>
+      <c r="T184" t="n">
+        <v>18</v>
+      </c>
+      <c r="U184" t="n">
+        <v>4</v>
+      </c>
+      <c r="V184" t="n">
+        <v>26</v>
+      </c>
+      <c r="W184" t="n">
+        <v>4</v>
+      </c>
+      <c r="X184" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD184" t="n">
         <v>3</v>
       </c>
-      <c r="N184" t="n">
+      <c r="AE184" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF184" t="n">
         <v>5</v>
       </c>
-      <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>9</v>
-      </c>
-      <c r="R184" t="n">
-        <v>5</v>
-      </c>
-      <c r="S184" t="n">
-        <v>8</v>
-      </c>
-      <c r="T184" t="n">
-        <v>3</v>
-      </c>
-      <c r="U184" t="n">
-        <v>17</v>
-      </c>
-      <c r="V184" t="n">
-        <v>8</v>
-      </c>
-      <c r="W184" t="n">
-        <v>11</v>
-      </c>
-      <c r="X184" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y184" t="n">
-        <v>49</v>
-      </c>
-      <c r="Z184" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>Viale dei Gladiatori, 2 / Via del Foro Italico, Roma</t>
-        </is>
-      </c>
-      <c r="AC184" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD184" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE184" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF184" t="n">
-        <v>3</v>
-      </c>
       <c r="AG184" t="n">
-        <v>3.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH184" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AI184" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="AJ184" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="AK184" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AL184" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AM184" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AN184" t="n">
-        <v>2.58</v>
+        <v>1.94</v>
       </c>
       <c r="AO184" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR184" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AS184" t="n">
-        <v>2.63</v>
+        <v>3.24</v>
       </c>
       <c r="AT184" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AU184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>470</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>21601</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV184" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW184" t="n">
+        <v>89</v>
+      </c>
+      <c r="BX184" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY184" t="n">
+        <v>156</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR184" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS184" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU184" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV184" t="n">
         <v>4</v>
       </c>
-      <c r="AV184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX184" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY184" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ184" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB184" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD184" t="n">
-        <v>33</v>
-      </c>
-      <c r="BE184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF184" t="n">
-        <v>35000</v>
-      </c>
-      <c r="BG184" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI184" t="n">
-        <v>7</v>
-      </c>
-      <c r="BJ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL184" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM184" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN184" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP184" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ184" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR184" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS184" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT184" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV184" t="n">
-        <v>49</v>
-      </c>
-      <c r="BW184" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX184" t="n">
-        <v>96</v>
-      </c>
-      <c r="BY184" t="n">
-        <v>86</v>
-      </c>
-      <c r="BZ184" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CA184" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="CB184" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="CC184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR184" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS184" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU184" t="n">
+      <c r="CW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX184" t="n">
         <v>14</v>
-      </c>
-      <c r="CV184" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX184" t="n">
-        <v>3</v>
       </c>
       <c r="CY184" t="n">
         <v>5</v>
       </c>
       <c r="CZ184" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="DA184" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="DB184" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="DC184" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="DD184" t="n">
-        <v>1.45</v>
+        <v>0.91</v>
       </c>
       <c r="DE184" t="n">
-        <v>0.73</v>
+        <v>2.4</v>
       </c>
       <c r="DF184" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG184" t="n">
-        <v>0.44</v>
+        <v>2.25</v>
       </c>
       <c r="DH184" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="DI184" t="n">
-        <v>0.67</v>
+        <v>2.29</v>
       </c>
       <c r="DJ184" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DK184" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DL184" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="DM184" t="n">
-        <v>1.17</v>
+        <v>1.76</v>
       </c>
       <c r="DN184" t="n">
-        <v>2.52</v>
+        <v>3.01</v>
       </c>
       <c r="DO184" t="n">
         <v>22</v>
@@ -88828,10 +88852,10 @@
         <v>1</v>
       </c>
       <c r="DR184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT184" t="b">
         <v>0</v>
@@ -88840,98 +88864,74 @@
         <v>0</v>
       </c>
       <c r="DV184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW184" t="n">
-        <v>4.73</v>
+        <v>3.11</v>
       </c>
       <c r="DX184" t="n">
-        <v>5.21</v>
+        <v>2.06</v>
       </c>
       <c r="DY184" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="DZ184" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA184" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="EA184" t="inlineStr"/>
       <c r="EB184" t="inlineStr"/>
-      <c r="EC184" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
+      <c r="EC184" t="inlineStr"/>
       <c r="ED184" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EE184" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EF184" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EG184" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EH184" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EI184" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="EJ184" t="inlineStr">
         <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EK184" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EL184" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EM184" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EN184" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EK184" t="inlineStr"/>
+      <c r="EL184" t="inlineStr"/>
+      <c r="EM184" t="inlineStr"/>
+      <c r="EN184" t="inlineStr"/>
       <c r="EO184" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EP184" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -89273,7 +89273,7 @@
         <v>1</v>
       </c>
       <c r="DE185" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF185" t="n">
         <v>1.22</v>
@@ -89303,7 +89303,7 @@
         <v>2.53</v>
       </c>
       <c r="DO185" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP185" t="b">
         <v>1</v>
@@ -90375,161 +90375,161 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F188" s="2" t="n">
         <v>46032.58333333334</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="n">
+        <v>8</v>
+      </c>
+      <c r="L188" t="n">
+        <v>11</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
         <v>4</v>
       </c>
-      <c r="K188" t="n">
-        <v>2</v>
-      </c>
-      <c r="L188" t="n">
-        <v>6</v>
-      </c>
-      <c r="M188" t="n">
-        <v>3</v>
-      </c>
-      <c r="N188" t="n">
-        <v>3</v>
-      </c>
       <c r="O188" t="n">
         <v>0</v>
       </c>
       <c r="P188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R188" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S188" t="n">
         <v>9</v>
       </c>
       <c r="T188" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U188" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V188" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W188" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X188" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>Dacia Arena</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>Piazza le Repubblica Argentina, 3, Udine</t>
+        </is>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA188" t="n">
         <v>3</v>
-      </c>
-      <c r="Y188" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z188" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sinigaglia, 3, Como</t>
-        </is>
-      </c>
-      <c r="AC188" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD188" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE188" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF188" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG188" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH188" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI188" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ188" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK188" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL188" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM188" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AN188" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO188" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AP188" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ188" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR188" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AS188" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AT188" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AU188" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX188" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY188" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ188" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA188" t="n">
-        <v>0</v>
       </c>
       <c r="BB188" t="n">
         <v>-1</v>
@@ -90538,13 +90538,13 @@
         <v>0</v>
       </c>
       <c r="BD188" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="BE188" t="n">
         <v>0</v>
       </c>
       <c r="BF188" t="n">
-        <v>11667</v>
+        <v>23186</v>
       </c>
       <c r="BG188" t="n">
         <v>2</v>
@@ -90553,178 +90553,178 @@
         <v>1</v>
       </c>
       <c r="BI188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL188" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BM188" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR188" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT188" t="n">
         <v>4</v>
       </c>
-      <c r="BN188" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ188" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR188" t="n">
+      <c r="BU188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV188" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW188" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX188" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY188" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ188" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA188" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CB188" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR188" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS188" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU188" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV188" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX188" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY188" t="n">
         <v>4</v>
       </c>
-      <c r="BS188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT188" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV188" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW188" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX188" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY188" t="n">
-        <v>61</v>
-      </c>
-      <c r="BZ188" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CA188" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB188" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CC188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR188" t="n">
-        <v>30</v>
-      </c>
-      <c r="CS188" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU188" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV188" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX188" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY188" t="n">
-        <v>15</v>
-      </c>
       <c r="CZ188" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="DA188" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="DB188" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="DC188" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="DD188" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="DE188" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DF188" t="n">
         <v>1.33</v>
       </c>
-      <c r="DF188" t="n">
-        <v>2.25</v>
-      </c>
       <c r="DG188" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="DH188" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="DI188" t="n">
-        <v>1.44</v>
+        <v>0.63</v>
       </c>
       <c r="DJ188" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="DK188" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="DL188" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="DM188" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="DN188" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="DO188" t="n">
         <v>22</v>
@@ -90736,10 +90736,10 @@
         <v>1</v>
       </c>
       <c r="DR188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT188" t="b">
         <v>0</v>
@@ -90751,95 +90751,95 @@
         <v>1</v>
       </c>
       <c r="DW188" t="n">
-        <v>5.01</v>
+        <v>5.73</v>
       </c>
       <c r="DX188" t="n">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="DY188" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ188" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA188" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EB188" t="inlineStr"/>
       <c r="EC188" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED188" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EE188" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EF188" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EG188" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH188" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EI188" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EJ188" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EK188" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL188" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EM188" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EN188" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EO188" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EP188" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -90859,161 +90859,161 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F189" s="2" t="n">
         <v>46032.58333333334</v>
       </c>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I189" t="n">
+        <v>2</v>
+      </c>
+      <c r="J189" t="n">
         <v>4</v>
       </c>
-      <c r="J189" t="n">
+      <c r="K189" t="n">
+        <v>2</v>
+      </c>
+      <c r="L189" t="n">
+        <v>6</v>
+      </c>
+      <c r="M189" t="n">
         <v>3</v>
       </c>
-      <c r="K189" t="n">
-        <v>8</v>
-      </c>
-      <c r="L189" t="n">
-        <v>11</v>
-      </c>
-      <c r="M189" t="n">
-        <v>1</v>
-      </c>
       <c r="N189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R189" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S189" t="n">
         <v>9</v>
       </c>
       <c r="T189" t="n">
+        <v>5</v>
+      </c>
+      <c r="U189" t="n">
+        <v>12</v>
+      </c>
+      <c r="V189" t="n">
         <v>7</v>
       </c>
-      <c r="U189" t="n">
-        <v>11</v>
-      </c>
-      <c r="V189" t="n">
+      <c r="W189" t="n">
         <v>14</v>
       </c>
-      <c r="W189" t="n">
-        <v>13</v>
-      </c>
       <c r="X189" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y189" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="Z189" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>Dacia Arena</t>
+          <t>Stadio Giuseppe Sinigaglia</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>Piazza le Repubblica Argentina, 3, Udine</t>
+          <t>Via Giuseppe Sinigaglia, 3, Como</t>
         </is>
       </c>
       <c r="AC189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG189" t="n">
         <v>4</v>
       </c>
-      <c r="AE189" t="n">
+      <c r="AH189" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK189" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF189" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG189" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AH189" t="n">
+      <c r="AL189" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ189" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI189" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ189" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK189" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL189" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM189" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN189" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO189" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AP189" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ189" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR189" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AS189" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AT189" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AU189" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY189" t="n">
         <v>1</v>
       </c>
       <c r="AZ189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB189" t="n">
         <v>-1</v>
@@ -91022,13 +91022,13 @@
         <v>0</v>
       </c>
       <c r="BD189" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="BE189" t="n">
         <v>0</v>
       </c>
       <c r="BF189" t="n">
-        <v>23186</v>
+        <v>11667</v>
       </c>
       <c r="BG189" t="n">
         <v>2</v>
@@ -91037,181 +91037,181 @@
         <v>1</v>
       </c>
       <c r="BI189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV189" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW189" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX189" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY189" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ189" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA189" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB189" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR189" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS189" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU189" t="n">
         <v>3</v>
       </c>
-      <c r="BJ189" t="n">
+      <c r="CV189" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX189" t="n">
         <v>3</v>
       </c>
-      <c r="BK189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL189" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM189" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN189" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR189" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT189" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV189" t="n">
-        <v>41</v>
-      </c>
-      <c r="BW189" t="n">
-        <v>41</v>
-      </c>
-      <c r="BX189" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY189" t="n">
-        <v>104</v>
-      </c>
-      <c r="BZ189" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="CA189" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CB189" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CC189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR189" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS189" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU189" t="n">
+      <c r="CY189" t="n">
         <v>15</v>
       </c>
-      <c r="CV189" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX189" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY189" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ189" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="DA189" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="DB189" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="DC189" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="DE189" t="n">
-        <v>0.64</v>
+        <v>1.33</v>
       </c>
       <c r="DF189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG189" t="n">
         <v>1.33</v>
       </c>
-      <c r="DG189" t="n">
-        <v>0.67</v>
-      </c>
       <c r="DH189" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="DI189" t="n">
-        <v>0.63</v>
+        <v>1.44</v>
       </c>
       <c r="DJ189" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="DK189" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="DL189" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="DM189" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="DN189" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="DO189" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -91220,10 +91220,10 @@
         <v>1</v>
       </c>
       <c r="DR189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT189" t="b">
         <v>0</v>
@@ -91235,95 +91235,95 @@
         <v>1</v>
       </c>
       <c r="DW189" t="n">
-        <v>5.73</v>
+        <v>5.01</v>
       </c>
       <c r="DX189" t="n">
-        <v>3.28</v>
+        <v>2.79</v>
       </c>
       <c r="DY189" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ189" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA189" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EB189" t="inlineStr"/>
       <c r="EC189" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED189" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE189" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EF189" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EG189" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH189" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EI189" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ189" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="EK189" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EL189" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EM189" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EN189" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EO189" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EP189" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -93582,7 +93582,7 @@
         <v>49</v>
       </c>
       <c r="DD194" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE194" t="n">
         <v>1.18</v>
@@ -93615,7 +93615,7 @@
         <v>2.55</v>
       </c>
       <c r="DO194" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP194" t="b">
         <v>1</v>
@@ -96406,7 +96406,7 @@
         <v>64</v>
       </c>
       <c r="DD200" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE200" t="n">
         <v>1.33</v>
@@ -96439,7 +96439,7 @@
         <v>2.54</v>
       </c>
       <c r="DO200" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP200" t="b">
         <v>1</v>
@@ -97883,7 +97883,7 @@
         <v>3.41</v>
       </c>
       <c r="DO203" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP203" t="b">
         <v>1</v>
@@ -101271,7 +101271,7 @@
         <v>2.29</v>
       </c>
       <c r="DO210" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP210" t="b">
         <v>0</v>
@@ -106068,6 +106068,482 @@
       <c r="EP220" t="inlineStr">
         <is>
           <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Italy_Serie_A_2025-2026</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>22</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>46048.82291666666</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>3</v>
+      </c>
+      <c r="I221" t="n">
+        <v>4</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="n">
+        <v>8</v>
+      </c>
+      <c r="L221" t="n">
+        <v>11</v>
+      </c>
+      <c r="M221" t="n">
+        <v>2</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>4</v>
+      </c>
+      <c r="R221" t="n">
+        <v>7</v>
+      </c>
+      <c r="S221" t="n">
+        <v>3</v>
+      </c>
+      <c r="T221" t="n">
+        <v>13</v>
+      </c>
+      <c r="U221" t="n">
+        <v>7</v>
+      </c>
+      <c r="V221" t="n">
+        <v>20</v>
+      </c>
+      <c r="W221" t="n">
+        <v>8</v>
+      </c>
+      <c r="X221" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>Piazzale Olimpia, Verona</t>
+        </is>
+      </c>
+      <c r="AC221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>466</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>18720</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV221" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW221" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX221" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY221" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ221" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA221" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CB221" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR221" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS221" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU221" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV221" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW221" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX221" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY221" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ221" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA221" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB221" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC221" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD221" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DE221" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DF221" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DG221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH221" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI221" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ221" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK221" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM221" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN221" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="DO221" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT221" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU221" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV221" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW221" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="DX221" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DY221" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="DZ221" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA221" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EB221" t="inlineStr"/>
+      <c r="EC221" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED221" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EE221" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EF221" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EG221" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH221" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EI221" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EJ221" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EK221" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL221" t="inlineStr"/>
+      <c r="EM221" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN221" t="inlineStr"/>
+      <c r="EO221" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP221" t="inlineStr">
+        <is>
+          <t>1.74</t>
         </is>
       </c>
     </row>
